--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DCD615B-37A9-4296-B913-9560B1BC50D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A5AC5D-8760-44BD-946D-6B94219E1FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5257" uniqueCount="4793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5276" uniqueCount="4817">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -14752,6 +14752,78 @@
   </si>
   <si>
     <t xml:space="preserve">El Terremoto de Caracas de 1967: 50 años después. </t>
+  </si>
+  <si>
+    <t>FUNVISIS. Publicaciones y documentos oficiales sobre riesgo sísmico y deslaves en Venezuela.</t>
+  </si>
+  <si>
+    <t>Bibliografía cronológica anotada. 2026. Preparado el 7 de Julio de 2026</t>
+  </si>
+  <si>
+    <t>Estudio sobre el Plan Básico de Prevención de Desastres en el Distrito Metropolitano de Caracas</t>
+  </si>
+  <si>
+    <t>Agencia de Cooperación Internacional de Japón (JICA). Pacific Consultant International en asociación con OYO International Corporation. Marzo 2005.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estudio de funciones receptoras de la estructura cortical del sector meridional de los Andes de Mérida. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saavedra, M.; Quinteros, C.; Schmitz, M.; Rendón, H.; Alvarado, L. </t>
+  </si>
+  <si>
+    <t>Revista de la Facultad de Ingeniería, Universidad Central de Venezuela, Volumen 36, Número 2, 2021.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">José Mas Vall (1918 - 2003). Destacado egresado de la Primera Promoción de Geólogos (1942), Escuela de Geología de la ilustre Universidad Central de Venezuela. </t>
+  </si>
+  <si>
+    <t>MAYA. Revista de Geociencias, Julio 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La odisea del hidrógeno: de curiosidad química a combustible del futuro. </t>
+  </si>
+  <si>
+    <t>Luis Angel Valencia Flores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Análisis multiescala de registros de pozos en campos de EEUU y Venezuela. </t>
+  </si>
+  <si>
+    <t>Rubymer Morán, Milagrosa Aldana, Ilich García, Sary Zambrano y José Baena</t>
+  </si>
+  <si>
+    <t>Revista de la Facultad de Ingeniería, Universidad Central de Venezuela, Volumen 36, Número 1, 2021</t>
+  </si>
+  <si>
+    <t>Application of Micropaleontology in Exploration Geology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan E. van Hinte </t>
+  </si>
+  <si>
+    <t>Geohistory Analysis, May 1988 – October 1989</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#FUNVISIS2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#Japan2005</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/geophysics.html#SaavedraMetal2021</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#CastroM2026c</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/topics.html#ValenzuelaLA2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/petrophysics.html#MoranRetal2021</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#vanHinteJE1989</t>
   </si>
 </sst>
 </file>
@@ -14847,7 +14919,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
@@ -14860,6 +14932,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -47066,13 +47139,13 @@
         <v>4716</v>
       </c>
       <c r="G1281" s="1" t="str">
-        <f t="shared" ref="G1281:G1305" si="41">HYPERLINK(F1281)</f>
+        <f t="shared" ref="G1281:G1312" si="41">HYPERLINK(F1281)</f>
         <v>https://mariantoc.github.io/minerals.html#Ayalaetal2010</v>
       </c>
     </row>
     <row r="1282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1282">
-        <f t="shared" ref="A1282:A1305" si="42">A1281+1</f>
+        <f t="shared" ref="A1282:A1312" si="42">A1281+1</f>
         <v>1281</v>
       </c>
       <c r="B1282" t="s">
@@ -47656,38 +47729,172 @@
       </c>
     </row>
     <row r="1306" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1306" s="7" t="s">
-        <v>4315</v>
+      <c r="A1306">
+        <f t="shared" si="42"/>
+        <v>1305</v>
+      </c>
+      <c r="B1306" t="s">
+        <v>4793</v>
+      </c>
+      <c r="D1306">
+        <v>2026</v>
+      </c>
+      <c r="E1306" t="s">
+        <v>4794</v>
+      </c>
+      <c r="F1306" s="8" t="s">
+        <v>4810</v>
+      </c>
+      <c r="G1306" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/biography.html#FUNVISIS2026</v>
       </c>
     </row>
     <row r="1307" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1307" s="7" t="s">
-        <v>4315</v>
+      <c r="A1307">
+        <f t="shared" si="42"/>
+        <v>1306</v>
+      </c>
+      <c r="B1307" t="s">
+        <v>4795</v>
+      </c>
+      <c r="D1307">
+        <v>2005</v>
+      </c>
+      <c r="E1307" t="s">
+        <v>4796</v>
+      </c>
+      <c r="F1307" s="8" t="s">
+        <v>4811</v>
+      </c>
+      <c r="G1307" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/biography.html#Japan2005</v>
       </c>
     </row>
     <row r="1308" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1308" s="7" t="s">
-        <v>4315</v>
+      <c r="A1308">
+        <f t="shared" si="42"/>
+        <v>1307</v>
+      </c>
+      <c r="B1308" t="s">
+        <v>4797</v>
+      </c>
+      <c r="C1308" t="s">
+        <v>4798</v>
+      </c>
+      <c r="D1308">
+        <v>2021</v>
+      </c>
+      <c r="E1308" t="s">
+        <v>4799</v>
+      </c>
+      <c r="F1308" s="8" t="s">
+        <v>4812</v>
+      </c>
+      <c r="G1308" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/geophysics.html#SaavedraMetal2021</v>
       </c>
     </row>
     <row r="1309" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1309" s="7" t="s">
-        <v>4315</v>
+      <c r="A1309">
+        <f t="shared" si="42"/>
+        <v>1308</v>
+      </c>
+      <c r="B1309" t="s">
+        <v>4800</v>
+      </c>
+      <c r="C1309" t="s">
+        <v>2880</v>
+      </c>
+      <c r="D1309">
+        <v>2026</v>
+      </c>
+      <c r="E1309" t="s">
+        <v>4801</v>
+      </c>
+      <c r="F1309" s="8" t="s">
+        <v>4813</v>
+      </c>
+      <c r="G1309" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/biography.html#CastroM2026c</v>
       </c>
     </row>
     <row r="1310" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1310" s="7" t="s">
-        <v>4315</v>
+      <c r="A1310">
+        <f t="shared" si="42"/>
+        <v>1309</v>
+      </c>
+      <c r="B1310" t="s">
+        <v>4802</v>
+      </c>
+      <c r="C1310" t="s">
+        <v>4803</v>
+      </c>
+      <c r="D1310">
+        <v>2026</v>
+      </c>
+      <c r="E1310" t="s">
+        <v>4801</v>
+      </c>
+      <c r="F1310" s="8" t="s">
+        <v>4814</v>
+      </c>
+      <c r="G1310" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/topics.html#ValenzuelaLA2026</v>
       </c>
     </row>
     <row r="1311" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1311" s="7" t="s">
-        <v>4315</v>
+      <c r="A1311">
+        <f t="shared" si="42"/>
+        <v>1310</v>
+      </c>
+      <c r="B1311" t="s">
+        <v>4804</v>
+      </c>
+      <c r="C1311" t="s">
+        <v>4805</v>
+      </c>
+      <c r="D1311">
+        <v>2021</v>
+      </c>
+      <c r="E1311" t="s">
+        <v>4806</v>
+      </c>
+      <c r="F1311" s="8" t="s">
+        <v>4815</v>
+      </c>
+      <c r="G1311" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/petrophysics.html#MoranRetal2021</v>
       </c>
     </row>
     <row r="1312" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1312" s="7" t="s">
-        <v>4315</v>
+      <c r="A1312">
+        <f t="shared" si="42"/>
+        <v>1311</v>
+      </c>
+      <c r="B1312" t="s">
+        <v>4807</v>
+      </c>
+      <c r="C1312" t="s">
+        <v>4808</v>
+      </c>
+      <c r="D1312">
+        <v>1989</v>
+      </c>
+      <c r="E1312" t="s">
+        <v>4809</v>
+      </c>
+      <c r="F1312" s="8" t="s">
+        <v>4816</v>
+      </c>
+      <c r="G1312" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#vanHinteJE1989</v>
       </c>
     </row>
     <row r="1313" spans="6:6" x14ac:dyDescent="0.3">

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A5AC5D-8760-44BD-946D-6B94219E1FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D4D69E-2827-4A74-BB6D-1F54A83B4EEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5276" uniqueCount="4817">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5296" uniqueCount="4841">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -14824,6 +14824,78 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/stratigraphy.html#vanHinteJE1989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atlas Sismológico de Venezuela. </t>
+  </si>
+  <si>
+    <t>50 Años de FUNVISIS (Fundación Venezolana de Investigaciones Sismológicas) 2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lecciones de los eventos sísmicos en Cuba occidental y norte de Venezuela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manuel A. Iturralde-Vinent y Enrique Arango Arias </t>
+  </si>
+  <si>
+    <t>Juventud Técnica, 12 de Julio de 2026. Juventud.web@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Guaire desbordado. </t>
+  </si>
+  <si>
+    <t>José Antonio Rodríguez Art</t>
+  </si>
+  <si>
+    <t>MAYA. Revista de Geociencias, pp. 40 – 42, Abril 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faustino Corsi y su catálogo de piedras ornamentales. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fórmulas facilitadoras en los cálculos del COT actual, COT original e índice de hidrógeno original (IH original). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">María del Carmen Gómez </t>
+  </si>
+  <si>
+    <t>Boletín de la Sociedad Venezolana de Geólogos, Volumen 27, Número 1, pp. 48 – 52, 2002</t>
+  </si>
+  <si>
+    <t>Parque Nacional Cerro Copey. Una joya ecológica y paisajista del oriente.</t>
+  </si>
+  <si>
+    <t>Juan Carlos Jácome</t>
+  </si>
+  <si>
+    <t>Carta Ecológica de Lagoven S.A., Número 50, Septiembre – Octubre, 1989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introducción a los Radiolarios. </t>
+  </si>
+  <si>
+    <t>Richard E. Casey</t>
+  </si>
+  <si>
+    <t>Curso de Micropaleontología Aplicada, Universidad Nacional Autónoma de México, Instituto de Geología, Octubre 6 a 26, 1980</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#FUNVISIS50</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#IturraldeMAArangoE2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#RodriguezJA2026b</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/geochemistry.html#GomezMC2002</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/ecology.html#JacomeJC1989</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#CaseyRE1980</t>
   </si>
 </sst>
 </file>
@@ -47139,13 +47211,13 @@
         <v>4716</v>
       </c>
       <c r="G1281" s="1" t="str">
-        <f t="shared" ref="G1281:G1312" si="41">HYPERLINK(F1281)</f>
+        <f t="shared" ref="G1281:G1319" si="41">HYPERLINK(F1281)</f>
         <v>https://mariantoc.github.io/minerals.html#Ayalaetal2010</v>
       </c>
     </row>
     <row r="1282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1282">
-        <f t="shared" ref="A1282:A1312" si="42">A1281+1</f>
+        <f t="shared" ref="A1282:A1319" si="42">A1281+1</f>
         <v>1281</v>
       </c>
       <c r="B1282" t="s">
@@ -47742,7 +47814,7 @@
       <c r="E1306" t="s">
         <v>4794</v>
       </c>
-      <c r="F1306" s="8" t="s">
+      <c r="F1306" t="s">
         <v>4810</v>
       </c>
       <c r="G1306" s="1" t="str">
@@ -47764,7 +47836,7 @@
       <c r="E1307" t="s">
         <v>4796</v>
       </c>
-      <c r="F1307" s="8" t="s">
+      <c r="F1307" t="s">
         <v>4811</v>
       </c>
       <c r="G1307" s="1" t="str">
@@ -47789,7 +47861,7 @@
       <c r="E1308" t="s">
         <v>4799</v>
       </c>
-      <c r="F1308" s="8" t="s">
+      <c r="F1308" t="s">
         <v>4812</v>
       </c>
       <c r="G1308" s="1" t="str">
@@ -47814,7 +47886,7 @@
       <c r="E1309" t="s">
         <v>4801</v>
       </c>
-      <c r="F1309" s="8" t="s">
+      <c r="F1309" t="s">
         <v>4813</v>
       </c>
       <c r="G1309" s="1" t="str">
@@ -47839,7 +47911,7 @@
       <c r="E1310" t="s">
         <v>4801</v>
       </c>
-      <c r="F1310" s="8" t="s">
+      <c r="F1310" t="s">
         <v>4814</v>
       </c>
       <c r="G1310" s="1" t="str">
@@ -47864,7 +47936,7 @@
       <c r="E1311" t="s">
         <v>4806</v>
       </c>
-      <c r="F1311" s="8" t="s">
+      <c r="F1311" t="s">
         <v>4815</v>
       </c>
       <c r="G1311" s="1" t="str">
@@ -47889,7 +47961,7 @@
       <c r="E1312" t="s">
         <v>4809</v>
       </c>
-      <c r="F1312" s="8" t="s">
+      <c r="F1312" t="s">
         <v>4816</v>
       </c>
       <c r="G1312" s="1" t="str">
@@ -47897,82 +47969,219 @@
         <v>https://mariantoc.github.io/stratigraphy.html#vanHinteJE1989</v>
       </c>
     </row>
-    <row r="1313" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1313" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1314" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1314" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1315" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1315" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1316" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1316" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1317" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1317" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1318" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1318" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1319" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1319" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1320" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1313" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1313">
+        <f t="shared" si="42"/>
+        <v>1312</v>
+      </c>
+      <c r="B1313" t="s">
+        <v>4817</v>
+      </c>
+      <c r="D1313">
+        <v>2022</v>
+      </c>
+      <c r="E1313" t="s">
+        <v>4818</v>
+      </c>
+      <c r="F1313" s="8" t="s">
+        <v>4835</v>
+      </c>
+      <c r="G1313" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/biography.html#FUNVISIS50</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1314">
+        <f t="shared" si="42"/>
+        <v>1313</v>
+      </c>
+      <c r="B1314" t="s">
+        <v>4819</v>
+      </c>
+      <c r="C1314" t="s">
+        <v>4820</v>
+      </c>
+      <c r="D1314">
+        <v>2026</v>
+      </c>
+      <c r="E1314" t="s">
+        <v>4821</v>
+      </c>
+      <c r="F1314" s="8" t="s">
+        <v>4836</v>
+      </c>
+      <c r="G1314" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/biography.html#IturraldeMAArangoE2026</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1315">
+        <f t="shared" si="42"/>
+        <v>1314</v>
+      </c>
+      <c r="B1315" t="s">
+        <v>4822</v>
+      </c>
+      <c r="C1315" t="s">
+        <v>4823</v>
+      </c>
+      <c r="D1315">
+        <v>2026</v>
+      </c>
+      <c r="E1315" t="s">
+        <v>4824</v>
+      </c>
+      <c r="F1315" s="8" t="s">
+        <v>4837</v>
+      </c>
+      <c r="G1315" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/biography.html#RodriguezJA2026b</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1316">
+        <f t="shared" si="42"/>
+        <v>1315</v>
+      </c>
+      <c r="B1316" t="s">
+        <v>4825</v>
+      </c>
+      <c r="C1316" t="s">
+        <v>2454</v>
+      </c>
+      <c r="D1316">
+        <v>2026</v>
+      </c>
+      <c r="E1316" t="s">
+        <v>4509</v>
+      </c>
+      <c r="F1316" s="8" t="s">
+        <v>4691</v>
+      </c>
+      <c r="G1316" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/biography.html#PorrasJS2026</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1317">
+        <f t="shared" si="42"/>
+        <v>1316</v>
+      </c>
+      <c r="B1317" t="s">
+        <v>4826</v>
+      </c>
+      <c r="C1317" t="s">
+        <v>4827</v>
+      </c>
+      <c r="D1317">
+        <v>2002</v>
+      </c>
+      <c r="E1317" t="s">
+        <v>4828</v>
+      </c>
+      <c r="F1317" s="8" t="s">
+        <v>4838</v>
+      </c>
+      <c r="G1317" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/geochemistry.html#GomezMC2002</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1318">
+        <f t="shared" si="42"/>
+        <v>1317</v>
+      </c>
+      <c r="B1318" t="s">
+        <v>4829</v>
+      </c>
+      <c r="C1318" t="s">
+        <v>4830</v>
+      </c>
+      <c r="D1318">
+        <v>1989</v>
+      </c>
+      <c r="E1318" t="s">
+        <v>4831</v>
+      </c>
+      <c r="F1318" s="8" t="s">
+        <v>4839</v>
+      </c>
+      <c r="G1318" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/ecology.html#JacomeJC1989</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1319">
+        <f t="shared" si="42"/>
+        <v>1318</v>
+      </c>
+      <c r="B1319" t="s">
+        <v>4832</v>
+      </c>
+      <c r="C1319" t="s">
+        <v>4833</v>
+      </c>
+      <c r="D1319">
+        <v>1980</v>
+      </c>
+      <c r="E1319" t="s">
+        <v>4834</v>
+      </c>
+      <c r="F1319" s="8" t="s">
+        <v>4840</v>
+      </c>
+      <c r="G1319" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#CaseyRE1980</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1320" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1321" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1321" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1321" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1322" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1322" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1322" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1323" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1323" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1323" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1324" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1324" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1324" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1325" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1325" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1325" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1326" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1326" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1326" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1327" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1327" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1327" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1328" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1328" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1328" s="7" t="s">
         <v>4315</v>
       </c>

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D4D69E-2827-4A74-BB6D-1F54A83B4EEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0666765D-9671-4BC1-9873-F03EE025B32C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5296" uniqueCount="4841">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5316" uniqueCount="4866">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -14896,6 +14896,81 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/stratigraphy.html#CaseyRE1980</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todo lo que se movió en 1812 en la Placa del Caribe: sismos, volcanes y transmisión de energía. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rogelio Altez </t>
+  </si>
+  <si>
+    <t>Revista Geográfica Venezolana, Número Especial 2005, pp. 143 – 170, 2005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geological sketch map of the Guiana Shield </t>
+  </si>
+  <si>
+    <t>Tomado de: The Geology of the Guiana Shield, A. K. Gibbs and C. N. Barron. Oxford Monographs on Geology and Geophysics, No. 22, 1993.</t>
+  </si>
+  <si>
+    <t>Caracterización de suelos con métodos geofísicos, estado Vargas (La Guaira, Macuto, Caraballeda y Tanaguarena).</t>
+  </si>
+  <si>
+    <t>Marcos Romero, Analia Cragno, Ricardo Ambrosio, Michael Schmitz y Jorge González</t>
+  </si>
+  <si>
+    <t>III Coloquio de Microzonificación Sísmica, Serie Técnica, Número 1, 2002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tropospheric correction using P y APS in the western region of Venezuela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gabriela Quintana Sánchez, Carlos Reinoza, Fikret Dogru, Gareth Funning and Frank Audemard </t>
+  </si>
+  <si>
+    <t>Geofísica Internacional, Vol. 65, No. 3, pp.2339 -2355, 2026</t>
+  </si>
+  <si>
+    <t>La importancia de la criptobioturbación en sucesiones sedimentarias del registro geológico.</t>
+  </si>
+  <si>
+    <t>MAYA. Revista de Geociencias, pp. 56 – 61, julio 2026</t>
+  </si>
+  <si>
+    <t>Macroforaminíferos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J. Butterlin </t>
+  </si>
+  <si>
+    <t>Los murciélagos y los cactus: una relación muy estrecha.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maricela Sosa y Pascual Soriano </t>
+  </si>
+  <si>
+    <t>Carta Ecológica de Lagoven S. A., Número 61, Abril – Junio, 1992</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#AltezR2025</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/maps.html#GibbsAKBarronCN1993</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/geophysics.html#RomeroMetal2002</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/geophysics.html#QuintanaGetal2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#CasasJE2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#ButterlinJ1982</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/ecology.html#SosaMSorianoP1992</t>
   </si>
 </sst>
 </file>
@@ -47211,13 +47286,13 @@
         <v>4716</v>
       </c>
       <c r="G1281" s="1" t="str">
-        <f t="shared" ref="G1281:G1319" si="41">HYPERLINK(F1281)</f>
+        <f t="shared" ref="G1281:G1326" si="41">HYPERLINK(F1281)</f>
         <v>https://mariantoc.github.io/minerals.html#Ayalaetal2010</v>
       </c>
     </row>
     <row r="1282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1282">
-        <f t="shared" ref="A1282:A1319" si="42">A1281+1</f>
+        <f t="shared" ref="A1282:A1326" si="42">A1281+1</f>
         <v>1281</v>
       </c>
       <c r="B1282" t="s">
@@ -47983,7 +48058,7 @@
       <c r="E1313" t="s">
         <v>4818</v>
       </c>
-      <c r="F1313" s="8" t="s">
+      <c r="F1313" t="s">
         <v>4835</v>
       </c>
       <c r="G1313" s="1" t="str">
@@ -48008,7 +48083,7 @@
       <c r="E1314" t="s">
         <v>4821</v>
       </c>
-      <c r="F1314" s="8" t="s">
+      <c r="F1314" t="s">
         <v>4836</v>
       </c>
       <c r="G1314" s="1" t="str">
@@ -48033,7 +48108,7 @@
       <c r="E1315" t="s">
         <v>4824</v>
       </c>
-      <c r="F1315" s="8" t="s">
+      <c r="F1315" t="s">
         <v>4837</v>
       </c>
       <c r="G1315" s="1" t="str">
@@ -48058,7 +48133,7 @@
       <c r="E1316" t="s">
         <v>4509</v>
       </c>
-      <c r="F1316" s="8" t="s">
+      <c r="F1316" t="s">
         <v>4691</v>
       </c>
       <c r="G1316" s="1" t="str">
@@ -48083,7 +48158,7 @@
       <c r="E1317" t="s">
         <v>4828</v>
       </c>
-      <c r="F1317" s="8" t="s">
+      <c r="F1317" t="s">
         <v>4838</v>
       </c>
       <c r="G1317" s="1" t="str">
@@ -48108,7 +48183,7 @@
       <c r="E1318" t="s">
         <v>4831</v>
       </c>
-      <c r="F1318" s="8" t="s">
+      <c r="F1318" t="s">
         <v>4839</v>
       </c>
       <c r="G1318" s="1" t="str">
@@ -48133,7 +48208,7 @@
       <c r="E1319" t="s">
         <v>4834</v>
       </c>
-      <c r="F1319" s="8" t="s">
+      <c r="F1319" t="s">
         <v>4840</v>
       </c>
       <c r="G1319" s="1" t="str">
@@ -48142,38 +48217,175 @@
       </c>
     </row>
     <row r="1320" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1320" s="7" t="s">
-        <v>4315</v>
+      <c r="A1320">
+        <f t="shared" si="42"/>
+        <v>1319</v>
+      </c>
+      <c r="B1320" t="s">
+        <v>4841</v>
+      </c>
+      <c r="C1320" t="s">
+        <v>4842</v>
+      </c>
+      <c r="D1320">
+        <v>2005</v>
+      </c>
+      <c r="E1320" t="s">
+        <v>4843</v>
+      </c>
+      <c r="F1320" s="8" t="s">
+        <v>4859</v>
+      </c>
+      <c r="G1320" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/biography.html#AltezR2025</v>
       </c>
     </row>
     <row r="1321" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1321" s="7" t="s">
-        <v>4315</v>
+      <c r="A1321">
+        <f t="shared" si="42"/>
+        <v>1320</v>
+      </c>
+      <c r="B1321" t="s">
+        <v>4844</v>
+      </c>
+      <c r="D1321">
+        <v>1993</v>
+      </c>
+      <c r="E1321" t="s">
+        <v>4845</v>
+      </c>
+      <c r="F1321" s="8" t="s">
+        <v>4860</v>
+      </c>
+      <c r="G1321" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/maps.html#GibbsAKBarronCN1993</v>
       </c>
     </row>
     <row r="1322" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1322" s="7" t="s">
-        <v>4315</v>
+      <c r="A1322">
+        <f t="shared" si="42"/>
+        <v>1321</v>
+      </c>
+      <c r="B1322" t="s">
+        <v>4846</v>
+      </c>
+      <c r="C1322" t="s">
+        <v>4847</v>
+      </c>
+      <c r="D1322">
+        <v>2002</v>
+      </c>
+      <c r="E1322" t="s">
+        <v>4848</v>
+      </c>
+      <c r="F1322" s="8" t="s">
+        <v>4861</v>
+      </c>
+      <c r="G1322" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/geophysics.html#RomeroMetal2002</v>
       </c>
     </row>
     <row r="1323" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1323" s="7" t="s">
-        <v>4315</v>
+      <c r="A1323">
+        <f t="shared" si="42"/>
+        <v>1322</v>
+      </c>
+      <c r="B1323" t="s">
+        <v>4849</v>
+      </c>
+      <c r="C1323" t="s">
+        <v>4850</v>
+      </c>
+      <c r="D1323">
+        <v>2026</v>
+      </c>
+      <c r="E1323" t="s">
+        <v>4851</v>
+      </c>
+      <c r="F1323" s="8" t="s">
+        <v>4862</v>
+      </c>
+      <c r="G1323" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/geophysics.html#QuintanaGetal2026</v>
       </c>
     </row>
     <row r="1324" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1324" s="7" t="s">
-        <v>4315</v>
+      <c r="A1324">
+        <f t="shared" si="42"/>
+        <v>1323</v>
+      </c>
+      <c r="B1324" t="s">
+        <v>4852</v>
+      </c>
+      <c r="C1324" t="s">
+        <v>2451</v>
+      </c>
+      <c r="D1324">
+        <v>2026</v>
+      </c>
+      <c r="E1324" t="s">
+        <v>4853</v>
+      </c>
+      <c r="F1324" s="8" t="s">
+        <v>4863</v>
+      </c>
+      <c r="G1324" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#CasasJE2026</v>
       </c>
     </row>
     <row r="1325" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1325" s="7" t="s">
-        <v>4315</v>
+      <c r="A1325">
+        <f t="shared" si="42"/>
+        <v>1324</v>
+      </c>
+      <c r="B1325" t="s">
+        <v>4854</v>
+      </c>
+      <c r="C1325" t="s">
+        <v>4855</v>
+      </c>
+      <c r="D1325">
+        <v>1982</v>
+      </c>
+      <c r="E1325" t="s">
+        <v>4834</v>
+      </c>
+      <c r="F1325" s="8" t="s">
+        <v>4864</v>
+      </c>
+      <c r="G1325" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#ButterlinJ1982</v>
       </c>
     </row>
     <row r="1326" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1326" s="7" t="s">
-        <v>4315</v>
+      <c r="A1326">
+        <f t="shared" si="42"/>
+        <v>1325</v>
+      </c>
+      <c r="B1326" t="s">
+        <v>4856</v>
+      </c>
+      <c r="C1326" t="s">
+        <v>4857</v>
+      </c>
+      <c r="D1326">
+        <v>1992</v>
+      </c>
+      <c r="E1326" t="s">
+        <v>4858</v>
+      </c>
+      <c r="F1326" s="8" t="s">
+        <v>4865</v>
+      </c>
+      <c r="G1326" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/ecology.html#SosaMSorianoP1992</v>
       </c>
     </row>
     <row r="1327" spans="1:7" x14ac:dyDescent="0.3">

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0666765D-9671-4BC1-9873-F03EE025B32C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C274F9E-5A71-41BE-B6D3-047F11EDEF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5316" uniqueCount="4866">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5336" uniqueCount="4891">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -14971,6 +14971,81 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/ecology.html#SosaMSorianoP1992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marine Diatoms. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lloyd M. Burckle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sobre la tierra que nos sacude y el estado que nos falla. </t>
+  </si>
+  <si>
+    <t>Josea Rondón</t>
+  </si>
+  <si>
+    <t>Artículo de Divulgación científica, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plaza de los Geólogos en Macuro, estado Sucre, Venezuela. Plaza didáctica donada a la población de Macuro, por la Promoción de Geólogos Víctor Petzall de la Universidad Central de Venezuela con el apoyo institucional de la Sociedad Venezolana de Geólogos. </t>
+  </si>
+  <si>
+    <t>MAYA. Revista de Geociencias, Agosto 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toxic rocks, a history from A to Z. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tim Carter </t>
+  </si>
+  <si>
+    <t>Geohistories. The magazine of the History of Geology Group, Number 73, pp. 16 – 17, April 2022</t>
+  </si>
+  <si>
+    <t>Mapa de las Provincias Geológicas de Guayana.</t>
+  </si>
+  <si>
+    <t>Tomado de: The Geology of the Guiana Shield, A. K. Gibbs and C. N. Barron. Oxford Monographs on Geology an Geophysics, No. 22, 1993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boscan Field, western Venezuela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">John A. Sutherland </t>
+  </si>
+  <si>
+    <t>Manuscript Chevron Oil Company, June 18, 1968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Síntesis paleogeográfica y petrolera del occidente de Venezuela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zambrano, E.; Vásquez, E.; Duval, B.; Latreille, M.; Coffinieres, B. </t>
+  </si>
+  <si>
+    <t>IV Congreso Geológico Venezolano, 16 – 22 de Noviembre de 1969</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#BurckleLM1982</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#RondonJ2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#CastroM2026d</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/topics.html#CarterT2022</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/maps.html#GibbsAK1987</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/fields.html#SutherlandJA1968</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#ZambranoEetal1971</t>
   </si>
 </sst>
 </file>
@@ -47286,13 +47361,13 @@
         <v>4716</v>
       </c>
       <c r="G1281" s="1" t="str">
-        <f t="shared" ref="G1281:G1326" si="41">HYPERLINK(F1281)</f>
+        <f t="shared" ref="G1281:G1333" si="41">HYPERLINK(F1281)</f>
         <v>https://mariantoc.github.io/minerals.html#Ayalaetal2010</v>
       </c>
     </row>
     <row r="1282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1282">
-        <f t="shared" ref="A1282:A1326" si="42">A1281+1</f>
+        <f t="shared" ref="A1282:A1333" si="42">A1281+1</f>
         <v>1281</v>
       </c>
       <c r="B1282" t="s">
@@ -48233,7 +48308,7 @@
       <c r="E1320" t="s">
         <v>4843</v>
       </c>
-      <c r="F1320" s="8" t="s">
+      <c r="F1320" t="s">
         <v>4859</v>
       </c>
       <c r="G1320" s="1" t="str">
@@ -48255,7 +48330,7 @@
       <c r="E1321" t="s">
         <v>4845</v>
       </c>
-      <c r="F1321" s="8" t="s">
+      <c r="F1321" t="s">
         <v>4860</v>
       </c>
       <c r="G1321" s="1" t="str">
@@ -48280,7 +48355,7 @@
       <c r="E1322" t="s">
         <v>4848</v>
       </c>
-      <c r="F1322" s="8" t="s">
+      <c r="F1322" t="s">
         <v>4861</v>
       </c>
       <c r="G1322" s="1" t="str">
@@ -48305,7 +48380,7 @@
       <c r="E1323" t="s">
         <v>4851</v>
       </c>
-      <c r="F1323" s="8" t="s">
+      <c r="F1323" t="s">
         <v>4862</v>
       </c>
       <c r="G1323" s="1" t="str">
@@ -48330,7 +48405,7 @@
       <c r="E1324" t="s">
         <v>4853</v>
       </c>
-      <c r="F1324" s="8" t="s">
+      <c r="F1324" t="s">
         <v>4863</v>
       </c>
       <c r="G1324" s="1" t="str">
@@ -48355,7 +48430,7 @@
       <c r="E1325" t="s">
         <v>4834</v>
       </c>
-      <c r="F1325" s="8" t="s">
+      <c r="F1325" t="s">
         <v>4864</v>
       </c>
       <c r="G1325" s="1" t="str">
@@ -48380,7 +48455,7 @@
       <c r="E1326" t="s">
         <v>4858</v>
       </c>
-      <c r="F1326" s="8" t="s">
+      <c r="F1326" t="s">
         <v>4865</v>
       </c>
       <c r="G1326" s="1" t="str">
@@ -48389,91 +48464,228 @@
       </c>
     </row>
     <row r="1327" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1327" s="7" t="s">
-        <v>4315</v>
+      <c r="A1327">
+        <f t="shared" si="42"/>
+        <v>1326</v>
+      </c>
+      <c r="B1327" t="s">
+        <v>4866</v>
+      </c>
+      <c r="C1327" t="s">
+        <v>4867</v>
+      </c>
+      <c r="D1327">
+        <v>1982</v>
+      </c>
+      <c r="E1327" t="s">
+        <v>4834</v>
+      </c>
+      <c r="F1327" s="8" t="s">
+        <v>4884</v>
+      </c>
+      <c r="G1327" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#BurckleLM1982</v>
       </c>
     </row>
     <row r="1328" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1328" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1329" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1329" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1330" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1330" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1331" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1331" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1332" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1332" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1333" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1333" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1334" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="A1328">
+        <f t="shared" si="42"/>
+        <v>1327</v>
+      </c>
+      <c r="B1328" t="s">
+        <v>4868</v>
+      </c>
+      <c r="C1328" t="s">
+        <v>4869</v>
+      </c>
+      <c r="D1328">
+        <v>2026</v>
+      </c>
+      <c r="E1328" t="s">
+        <v>4870</v>
+      </c>
+      <c r="F1328" s="8" t="s">
+        <v>4885</v>
+      </c>
+      <c r="G1328" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/biography.html#RondonJ2026</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1329">
+        <f t="shared" si="42"/>
+        <v>1328</v>
+      </c>
+      <c r="B1329" t="s">
+        <v>4871</v>
+      </c>
+      <c r="C1329" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1329">
+        <v>2026</v>
+      </c>
+      <c r="E1329" t="s">
+        <v>4872</v>
+      </c>
+      <c r="F1329" s="8" t="s">
+        <v>4886</v>
+      </c>
+      <c r="G1329" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/biography.html#CastroM2026d</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1330">
+        <f t="shared" si="42"/>
+        <v>1329</v>
+      </c>
+      <c r="B1330" t="s">
+        <v>4873</v>
+      </c>
+      <c r="C1330" t="s">
+        <v>4874</v>
+      </c>
+      <c r="D1330">
+        <v>2022</v>
+      </c>
+      <c r="E1330" t="s">
+        <v>4875</v>
+      </c>
+      <c r="F1330" s="8" t="s">
+        <v>4887</v>
+      </c>
+      <c r="G1330" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/topics.html#CarterT2022</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1331">
+        <f t="shared" si="42"/>
+        <v>1330</v>
+      </c>
+      <c r="B1331" t="s">
+        <v>4876</v>
+      </c>
+      <c r="D1331">
+        <v>1993</v>
+      </c>
+      <c r="E1331" t="s">
+        <v>4877</v>
+      </c>
+      <c r="F1331" s="8" t="s">
+        <v>4888</v>
+      </c>
+      <c r="G1331" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/maps.html#GibbsAK1987</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1332">
+        <f t="shared" si="42"/>
+        <v>1331</v>
+      </c>
+      <c r="B1332" t="s">
+        <v>4878</v>
+      </c>
+      <c r="C1332" t="s">
+        <v>4879</v>
+      </c>
+      <c r="D1332">
+        <v>1968</v>
+      </c>
+      <c r="E1332" t="s">
+        <v>4880</v>
+      </c>
+      <c r="F1332" s="8" t="s">
+        <v>4889</v>
+      </c>
+      <c r="G1332" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/fields.html#SutherlandJA1968</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1333">
+        <f t="shared" si="42"/>
+        <v>1332</v>
+      </c>
+      <c r="B1333" t="s">
+        <v>4881</v>
+      </c>
+      <c r="C1333" t="s">
+        <v>4882</v>
+      </c>
+      <c r="D1333">
+        <v>1971</v>
+      </c>
+      <c r="E1333" t="s">
+        <v>4883</v>
+      </c>
+      <c r="F1333" s="8" t="s">
+        <v>4890</v>
+      </c>
+      <c r="G1333" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#ZambranoEetal1971</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1334" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1335" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1335" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1335" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1336" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1336" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1336" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1337" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1337" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1337" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1338" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1338" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1338" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1339" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1339" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1339" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1340" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1340" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1340" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1341" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1341" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1341" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1342" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1342" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1342" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1343" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1343" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1343" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1344" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1344" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1344" s="7" t="s">
         <v>4315</v>
       </c>

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C274F9E-5A71-41BE-B6D3-047F11EDEF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9120671-A1B6-42D1-BA74-778AD7284864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5336" uniqueCount="4891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5350" uniqueCount="4909">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -15046,6 +15046,60 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/stratigraphy.html#ZambranoEetal1971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcareous nannofossils in marine sediments. </t>
+  </si>
+  <si>
+    <t>Stefan Gardner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catálogo de la Fauna Venezolana: Sarcodina, Rhizopoda, Foraminiferida. </t>
+  </si>
+  <si>
+    <t>Jaime Tello</t>
+  </si>
+  <si>
+    <t>America Association for the Advancement of Science, Marine Biological Association of the United Kingdom, New York Academy of Science, Sociedad Venezolana de Ciencias Naturales y Sociedad de Ciencias Naturales La Salle. Editorial Sucre, Caracas, 1981.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geology of Venezuela and its oil fields. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mencher, H. F.; Fichter, H. J.; Renz, H. H.; Wallis, W. E.; Petterson, J. M.; Robie, R. H. </t>
+  </si>
+  <si>
+    <t>Bulletin of the American Association of Petroleum Geologist, Vol.37, No. 4, pp. 690 – 777, April 1953</t>
+  </si>
+  <si>
+    <t>Impacto y prevención de inundaciones y aludes torrenciales en el Valle de Caracas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">José Luis López S. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lineament and structure map of the Guiana Shield. </t>
+  </si>
+  <si>
+    <t>Compiled by A. K. Gibbs 1987. In: The Geology of the Guiana Shield, A. K. Gibbs and C. N. Barron. Oxford Monographs on Geology and Geophysics, No. 22, 1993</t>
+  </si>
+  <si>
+    <t>Informe Final, Volumen 1. Instituto Mecánica de Fluidos (IMF), Universidad Central de Venezuela, Facultad de Ingeniería, Instituto de Mecánica de Fluidos, Junio 2006</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#GardnerS1982</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#TelloJ1981</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/fields.html#MencherHetal1953</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#LopezJL2006</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/maps.html#GibbsAK1987a</t>
   </si>
 </sst>
 </file>
@@ -47361,13 +47415,13 @@
         <v>4716</v>
       </c>
       <c r="G1281" s="1" t="str">
-        <f t="shared" ref="G1281:G1333" si="41">HYPERLINK(F1281)</f>
+        <f t="shared" ref="G1281:G1338" si="41">HYPERLINK(F1281)</f>
         <v>https://mariantoc.github.io/minerals.html#Ayalaetal2010</v>
       </c>
     </row>
     <row r="1282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1282">
-        <f t="shared" ref="A1282:A1333" si="42">A1281+1</f>
+        <f t="shared" ref="A1282:A1338" si="42">A1281+1</f>
         <v>1281</v>
       </c>
       <c r="B1282" t="s">
@@ -48480,7 +48534,7 @@
       <c r="E1327" t="s">
         <v>4834</v>
       </c>
-      <c r="F1327" s="8" t="s">
+      <c r="F1327" t="s">
         <v>4884</v>
       </c>
       <c r="G1327" s="1" t="str">
@@ -48505,7 +48559,7 @@
       <c r="E1328" t="s">
         <v>4870</v>
       </c>
-      <c r="F1328" s="8" t="s">
+      <c r="F1328" t="s">
         <v>4885</v>
       </c>
       <c r="G1328" s="1" t="str">
@@ -48530,7 +48584,7 @@
       <c r="E1329" t="s">
         <v>4872</v>
       </c>
-      <c r="F1329" s="8" t="s">
+      <c r="F1329" t="s">
         <v>4886</v>
       </c>
       <c r="G1329" s="1" t="str">
@@ -48555,7 +48609,7 @@
       <c r="E1330" t="s">
         <v>4875</v>
       </c>
-      <c r="F1330" s="8" t="s">
+      <c r="F1330" t="s">
         <v>4887</v>
       </c>
       <c r="G1330" s="1" t="str">
@@ -48577,7 +48631,7 @@
       <c r="E1331" t="s">
         <v>4877</v>
       </c>
-      <c r="F1331" s="8" t="s">
+      <c r="F1331" t="s">
         <v>4888</v>
       </c>
       <c r="G1331" s="1" t="str">
@@ -48602,7 +48656,7 @@
       <c r="E1332" t="s">
         <v>4880</v>
       </c>
-      <c r="F1332" s="8" t="s">
+      <c r="F1332" t="s">
         <v>4889</v>
       </c>
       <c r="G1332" s="1" t="str">
@@ -48627,7 +48681,7 @@
       <c r="E1333" t="s">
         <v>4883</v>
       </c>
-      <c r="F1333" s="8" t="s">
+      <c r="F1333" t="s">
         <v>4890</v>
       </c>
       <c r="G1333" s="1" t="str">
@@ -48636,28 +48690,125 @@
       </c>
     </row>
     <row r="1334" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1334" s="7" t="s">
-        <v>4315</v>
+      <c r="A1334">
+        <f t="shared" si="42"/>
+        <v>1333</v>
+      </c>
+      <c r="B1334" t="s">
+        <v>4891</v>
+      </c>
+      <c r="C1334" t="s">
+        <v>4892</v>
+      </c>
+      <c r="D1334">
+        <v>1982</v>
+      </c>
+      <c r="E1334" t="s">
+        <v>4834</v>
+      </c>
+      <c r="F1334" s="8" t="s">
+        <v>4904</v>
+      </c>
+      <c r="G1334" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#GardnerS1982</v>
       </c>
     </row>
     <row r="1335" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1335" s="7" t="s">
-        <v>4315</v>
+      <c r="A1335">
+        <f t="shared" si="42"/>
+        <v>1334</v>
+      </c>
+      <c r="B1335" t="s">
+        <v>4893</v>
+      </c>
+      <c r="C1335" t="s">
+        <v>4894</v>
+      </c>
+      <c r="D1335">
+        <v>1981</v>
+      </c>
+      <c r="E1335" t="s">
+        <v>4895</v>
+      </c>
+      <c r="F1335" s="8" t="s">
+        <v>4905</v>
+      </c>
+      <c r="G1335" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#TelloJ1981</v>
       </c>
     </row>
     <row r="1336" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1336" s="7" t="s">
-        <v>4315</v>
+      <c r="A1336">
+        <f t="shared" si="42"/>
+        <v>1335</v>
+      </c>
+      <c r="B1336" t="s">
+        <v>4896</v>
+      </c>
+      <c r="C1336" t="s">
+        <v>4897</v>
+      </c>
+      <c r="D1336">
+        <v>1953</v>
+      </c>
+      <c r="E1336" t="s">
+        <v>4898</v>
+      </c>
+      <c r="F1336" s="8" t="s">
+        <v>4906</v>
+      </c>
+      <c r="G1336" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/fields.html#MencherHetal1953</v>
       </c>
     </row>
     <row r="1337" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1337" s="7" t="s">
-        <v>4315</v>
+      <c r="A1337">
+        <f t="shared" si="42"/>
+        <v>1336</v>
+      </c>
+      <c r="B1337" t="s">
+        <v>4899</v>
+      </c>
+      <c r="C1337" t="s">
+        <v>4900</v>
+      </c>
+      <c r="D1337">
+        <v>2006</v>
+      </c>
+      <c r="E1337" t="s">
+        <v>4903</v>
+      </c>
+      <c r="F1337" s="8" t="s">
+        <v>4907</v>
+      </c>
+      <c r="G1337" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/biography.html#LopezJL2006</v>
       </c>
     </row>
     <row r="1338" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1338" s="7" t="s">
-        <v>4315</v>
+      <c r="A1338">
+        <f t="shared" si="42"/>
+        <v>1337</v>
+      </c>
+      <c r="B1338" t="s">
+        <v>4901</v>
+      </c>
+      <c r="D1338">
+        <v>1987</v>
+      </c>
+      <c r="E1338" t="s">
+        <v>4902</v>
+      </c>
+      <c r="F1338" s="8" t="s">
+        <v>4908</v>
+      </c>
+      <c r="G1338" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/maps.html#GibbsAK1987a</v>
       </c>
     </row>
     <row r="1339" spans="1:7" x14ac:dyDescent="0.3">

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9120671-A1B6-42D1-BA74-778AD7284864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C6837F4-E469-4204-ADDC-2939F4572978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5350" uniqueCount="4909">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5346" uniqueCount="4905">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -15063,15 +15063,6 @@
     <t>America Association for the Advancement of Science, Marine Biological Association of the United Kingdom, New York Academy of Science, Sociedad Venezolana de Ciencias Naturales y Sociedad de Ciencias Naturales La Salle. Editorial Sucre, Caracas, 1981.</t>
   </si>
   <si>
-    <t xml:space="preserve">Geology of Venezuela and its oil fields. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mencher, H. F.; Fichter, H. J.; Renz, H. H.; Wallis, W. E.; Petterson, J. M.; Robie, R. H. </t>
-  </si>
-  <si>
-    <t>Bulletin of the American Association of Petroleum Geologist, Vol.37, No. 4, pp. 690 – 777, April 1953</t>
-  </si>
-  <si>
     <t>Impacto y prevención de inundaciones y aludes torrenciales en el Valle de Caracas.</t>
   </si>
   <si>
@@ -15091,9 +15082,6 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/stratigraphy.html#TelloJ1981</t>
-  </si>
-  <si>
-    <t>https://mariantoc.github.io/fields.html#MencherHetal1953</t>
   </si>
   <si>
     <t>https://mariantoc.github.io/biography.html#LopezJL2006</t>
@@ -15195,7 +15183,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
@@ -15208,7 +15196,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -15524,7 +15511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B496A77-4B74-49B4-B08F-A7274E320005}">
-  <dimension ref="A1:H1380"/>
+  <dimension ref="A1:H1379"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="66.5546875" customWidth="1"/>
@@ -47415,13 +47402,13 @@
         <v>4716</v>
       </c>
       <c r="G1281" s="1" t="str">
-        <f t="shared" ref="G1281:G1338" si="41">HYPERLINK(F1281)</f>
+        <f t="shared" ref="G1281:G1337" si="41">HYPERLINK(F1281)</f>
         <v>https://mariantoc.github.io/minerals.html#Ayalaetal2010</v>
       </c>
     </row>
     <row r="1282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1282">
-        <f t="shared" ref="A1282:A1338" si="42">A1281+1</f>
+        <f t="shared" ref="A1282:A1337" si="42">A1281+1</f>
         <v>1281</v>
       </c>
       <c r="B1282" t="s">
@@ -48706,8 +48693,8 @@
       <c r="E1334" t="s">
         <v>4834</v>
       </c>
-      <c r="F1334" s="8" t="s">
-        <v>4904</v>
+      <c r="F1334" t="s">
+        <v>4901</v>
       </c>
       <c r="G1334" s="1" t="str">
         <f t="shared" si="41"/>
@@ -48731,8 +48718,8 @@
       <c r="E1335" t="s">
         <v>4895</v>
       </c>
-      <c r="F1335" s="8" t="s">
-        <v>4905</v>
+      <c r="F1335" t="s">
+        <v>4902</v>
       </c>
       <c r="G1335" s="1" t="str">
         <f t="shared" si="41"/>
@@ -48751,17 +48738,17 @@
         <v>4897</v>
       </c>
       <c r="D1336">
-        <v>1953</v>
+        <v>2006</v>
       </c>
       <c r="E1336" t="s">
-        <v>4898</v>
-      </c>
-      <c r="F1336" s="8" t="s">
-        <v>4906</v>
+        <v>4900</v>
+      </c>
+      <c r="F1336" t="s">
+        <v>4903</v>
       </c>
       <c r="G1336" s="1" t="str">
         <f t="shared" si="41"/>
-        <v>https://mariantoc.github.io/fields.html#MencherHetal1953</v>
+        <v>https://mariantoc.github.io/biography.html#LopezJL2006</v>
       </c>
     </row>
     <row r="1337" spans="1:7" x14ac:dyDescent="0.3">
@@ -48770,45 +48757,25 @@
         <v>1336</v>
       </c>
       <c r="B1337" t="s">
+        <v>4898</v>
+      </c>
+      <c r="D1337">
+        <v>1987</v>
+      </c>
+      <c r="E1337" t="s">
         <v>4899</v>
       </c>
-      <c r="C1337" t="s">
-        <v>4900</v>
-      </c>
-      <c r="D1337">
-        <v>2006</v>
-      </c>
-      <c r="E1337" t="s">
-        <v>4903</v>
-      </c>
-      <c r="F1337" s="8" t="s">
-        <v>4907</v>
+      <c r="F1337" t="s">
+        <v>4904</v>
       </c>
       <c r="G1337" s="1" t="str">
         <f t="shared" si="41"/>
-        <v>https://mariantoc.github.io/biography.html#LopezJL2006</v>
+        <v>https://mariantoc.github.io/maps.html#GibbsAK1987a</v>
       </c>
     </row>
     <row r="1338" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1338">
-        <f t="shared" si="42"/>
-        <v>1337</v>
-      </c>
-      <c r="B1338" t="s">
-        <v>4901</v>
-      </c>
-      <c r="D1338">
-        <v>1987</v>
-      </c>
-      <c r="E1338" t="s">
-        <v>4902</v>
-      </c>
-      <c r="F1338" s="8" t="s">
-        <v>4908</v>
-      </c>
-      <c r="G1338" s="1" t="str">
-        <f t="shared" si="41"/>
-        <v>https://mariantoc.github.io/maps.html#GibbsAK1987a</v>
+      <c r="F1338" s="7" t="s">
+        <v>4315</v>
       </c>
     </row>
     <row r="1339" spans="1:7" x14ac:dyDescent="0.3">
@@ -49013,11 +48980,6 @@
     </row>
     <row r="1379" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1379" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1380" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1380" s="7" t="s">
         <v>4315</v>
       </c>
     </row>

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C6837F4-E469-4204-ADDC-2939F4572978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{502D09C7-37D5-4A50-8186-7DEAE165FE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5346" uniqueCount="4905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5366" uniqueCount="4932">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -15088,6 +15088,87 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/maps.html#GibbsAK1987a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Universidad de Oriente (UDO) crea la cátedra Faja Petrolífera del Orinoco impulsada por la Sociedad Franco- Venezolana de Ingenieros y Científicos (DEVIC) y el Centro Latinoamericano y Caribeño de Estudios Energéticos y Ambientales (CELCEA) afiliado bajo un convenio de cooperación académica con la Universidad Latinoamericana del Caribe (ULAC). </t>
+  </si>
+  <si>
+    <t>Jhonny Márquez y Mario Zambrano Guichane</t>
+  </si>
+  <si>
+    <t>Información enviada a Notas de Geología de Venezuela por el profesor Mario Zambrano Guichane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresh Water Diatoms. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">J. Platt Bradbury </t>
+  </si>
+  <si>
+    <t>Curso de Micropaleontología Aplicada, Universidad Nacional Autónoma de México, Instituto de Geología, Octubre 6 a 26, 1980.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jean François Stephan </t>
+  </si>
+  <si>
+    <t>V Congreso Geológico Venezolano, Caracas, 19 al 23 de Noviembre de 1977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guía de la Excursión Geológica a la Isla de Margarita. </t>
+  </si>
+  <si>
+    <t>Excursión geológica auspiciada por la Sociedad Venezolana de Geólogos, realizada del 8 al 10 de Abril de 1983</t>
+  </si>
+  <si>
+    <t>Bellizzia, A.; Muñoz, N. G.; Macsotay, O.; Key, C.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El contacto cadena Caribe – Andes Merideños entre Carora y El Tocuyo, estado Lara: Observaciones sobre el estilo y la edad de las deformaciones Cenozoicas en el occidente venezolano. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dinoflagelados de la región nor-oriental de Venezuela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amelia La Barbera Sánchez </t>
+  </si>
+  <si>
+    <t>FONAIAP. Fondo Nacional de Investigaciones Agropecuarias, Cumaná, estado Sucre, Venezuela, 1991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carbonate depositional styles controlled by siliciclastic influx and relative sea level changes, Lower Cretaceous, central Lake Maracaibo, Venezuela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Izaskun Azpiritxaga </t>
+  </si>
+  <si>
+    <t>Thesis presented to the Faculty of the Graduate School of the University of Texas at Austin. In partial fulfillment of the requirements for the degree of Master of Arts, 1991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Area bajo régimen de administración especial. Guatopo resguarda la selva húmeda tropical venezolana </t>
+  </si>
+  <si>
+    <t>Carta Ecológica de Lagoven S.A., Número 48, Mayo – Junio, 1989</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#PlatJ1980</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#MarquezJZambranoM2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/structural.html#StephanJF1977</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/excursions.html#BelliziaAetal1983</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#LaBarberaA1991</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#AzpiritxagaI1991</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/ecology.html#Guatopo1989</t>
   </si>
 </sst>
 </file>
@@ -15183,7 +15264,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
@@ -15196,6 +15277,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -47402,13 +47484,13 @@
         <v>4716</v>
       </c>
       <c r="G1281" s="1" t="str">
-        <f t="shared" ref="G1281:G1337" si="41">HYPERLINK(F1281)</f>
+        <f t="shared" ref="G1281:G1344" si="41">HYPERLINK(F1281)</f>
         <v>https://mariantoc.github.io/minerals.html#Ayalaetal2010</v>
       </c>
     </row>
     <row r="1282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1282">
-        <f t="shared" ref="A1282:A1337" si="42">A1281+1</f>
+        <f t="shared" ref="A1282:A1344" si="42">A1281+1</f>
         <v>1281</v>
       </c>
       <c r="B1282" t="s">
@@ -48774,38 +48856,175 @@
       </c>
     </row>
     <row r="1338" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1338" s="7" t="s">
-        <v>4315</v>
+      <c r="A1338">
+        <f t="shared" si="42"/>
+        <v>1337</v>
+      </c>
+      <c r="B1338" t="s">
+        <v>4905</v>
+      </c>
+      <c r="C1338" t="s">
+        <v>4906</v>
+      </c>
+      <c r="D1338">
+        <v>2026</v>
+      </c>
+      <c r="E1338" t="s">
+        <v>4907</v>
+      </c>
+      <c r="F1338" s="8" t="s">
+        <v>4926</v>
+      </c>
+      <c r="G1338" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/biography.html#MarquezJZambranoM2026</v>
       </c>
     </row>
     <row r="1339" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1339" s="7" t="s">
-        <v>4315</v>
+      <c r="A1339">
+        <f t="shared" si="42"/>
+        <v>1338</v>
+      </c>
+      <c r="B1339" t="s">
+        <v>4908</v>
+      </c>
+      <c r="C1339" t="s">
+        <v>4909</v>
+      </c>
+      <c r="D1339">
+        <v>1980</v>
+      </c>
+      <c r="E1339" t="s">
+        <v>4910</v>
+      </c>
+      <c r="F1339" s="8" t="s">
+        <v>4925</v>
+      </c>
+      <c r="G1339" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#PlatJ1980</v>
       </c>
     </row>
     <row r="1340" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1340" s="7" t="s">
-        <v>4315</v>
+      <c r="A1340">
+        <f t="shared" si="42"/>
+        <v>1339</v>
+      </c>
+      <c r="B1340" t="s">
+        <v>4916</v>
+      </c>
+      <c r="C1340" t="s">
+        <v>4911</v>
+      </c>
+      <c r="D1340">
+        <v>1977</v>
+      </c>
+      <c r="E1340" t="s">
+        <v>4912</v>
+      </c>
+      <c r="F1340" s="8" t="s">
+        <v>4927</v>
+      </c>
+      <c r="G1340" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/structural.html#StephanJF1977</v>
       </c>
     </row>
     <row r="1341" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1341" s="7" t="s">
-        <v>4315</v>
+      <c r="A1341">
+        <f t="shared" si="42"/>
+        <v>1340</v>
+      </c>
+      <c r="B1341" t="s">
+        <v>4913</v>
+      </c>
+      <c r="C1341" t="s">
+        <v>4915</v>
+      </c>
+      <c r="D1341">
+        <v>1983</v>
+      </c>
+      <c r="E1341" t="s">
+        <v>4914</v>
+      </c>
+      <c r="F1341" s="8" t="s">
+        <v>4928</v>
+      </c>
+      <c r="G1341" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/excursions.html#BelliziaAetal1983</v>
       </c>
     </row>
     <row r="1342" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1342" s="7" t="s">
-        <v>4315</v>
+      <c r="A1342">
+        <f t="shared" si="42"/>
+        <v>1341</v>
+      </c>
+      <c r="B1342" t="s">
+        <v>4917</v>
+      </c>
+      <c r="C1342" t="s">
+        <v>4918</v>
+      </c>
+      <c r="D1342">
+        <v>1991</v>
+      </c>
+      <c r="E1342" t="s">
+        <v>4919</v>
+      </c>
+      <c r="F1342" s="8" t="s">
+        <v>4929</v>
+      </c>
+      <c r="G1342" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#LaBarberaA1991</v>
       </c>
     </row>
     <row r="1343" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1343" s="7" t="s">
-        <v>4315</v>
+      <c r="A1343">
+        <f t="shared" si="42"/>
+        <v>1342</v>
+      </c>
+      <c r="B1343" t="s">
+        <v>4920</v>
+      </c>
+      <c r="C1343" t="s">
+        <v>4921</v>
+      </c>
+      <c r="D1343">
+        <v>1991</v>
+      </c>
+      <c r="E1343" t="s">
+        <v>4922</v>
+      </c>
+      <c r="F1343" s="8" t="s">
+        <v>4930</v>
+      </c>
+      <c r="G1343" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#AzpiritxagaI1991</v>
       </c>
     </row>
     <row r="1344" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1344" s="7" t="s">
-        <v>4315</v>
+      <c r="A1344">
+        <f t="shared" si="42"/>
+        <v>1343</v>
+      </c>
+      <c r="B1344" t="s">
+        <v>4923</v>
+      </c>
+      <c r="D1344">
+        <v>1989</v>
+      </c>
+      <c r="E1344" t="s">
+        <v>4924</v>
+      </c>
+      <c r="F1344" s="8" t="s">
+        <v>4931</v>
+      </c>
+      <c r="G1344" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/ecology.html#Guatopo1989</v>
       </c>
     </row>
     <row r="1345" spans="6:6" x14ac:dyDescent="0.3">

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{502D09C7-37D5-4A50-8186-7DEAE165FE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B9C7C7-6811-4ABC-A98D-1D1366CE4DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5366" uniqueCount="4932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5387" uniqueCount="4957">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -15169,6 +15169,81 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/ecology.html#Guatopo1989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planktonic Foraminifera. </t>
+  </si>
+  <si>
+    <t>Curso de Micropaleontología Aplicada, Universidad Nacional Autónoma de México, Instituto de Geología, Octubre 6 a 26, 1982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guidebook to de geology of Machiques highway and Rio Negro, Distrito Perija, Zulia State, Venezuela. </t>
+  </si>
+  <si>
+    <t>John B. Miller</t>
+  </si>
+  <si>
+    <t>Sociedad Geológica de Venezuela Occidental, fieldtrip, April 11 and 12, 1959</t>
+  </si>
+  <si>
+    <t>En peligro el pulmón vegetal del mundo.</t>
+  </si>
+  <si>
+    <t>Carta Ecológica Lagoven S.A., Número 50, Septiembre – Octubre, 1989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flora Emblemática de Venezuela. </t>
+  </si>
+  <si>
+    <t>Jesús Hoyos</t>
+  </si>
+  <si>
+    <t>Publicación de Petróleos de Venezuela, Caracas, Venezuela, 30 de noviembre de 1985</t>
+  </si>
+  <si>
+    <t>Revised seismic history of the El Pilar fault, northeastern Venezuela, from the Cariaco 1997 earthquake and recent preliminary paleoseismic results.</t>
+  </si>
+  <si>
+    <t>Franck Audemard</t>
+  </si>
+  <si>
+    <t>Journal of Seismology: 11, pp. 311–326, 2007</t>
+  </si>
+  <si>
+    <t>The Orinoco Oil Belt, Venezuela.</t>
+  </si>
+  <si>
+    <t>Journal of Petroleum Geology, Vol. 10, No. 2, pp. 125 – 134, 1987</t>
+  </si>
+  <si>
+    <t>Interpretación integrada de anomalías gravimétricas y magnéticas a partir de datos satelitales en el Escudo de Guayana: estados Bolívar y Amazonas.</t>
+  </si>
+  <si>
+    <t>Inírida Rodríguez Millán</t>
+  </si>
+  <si>
+    <t>Boletín de la Academia Nacional de la Ingeniería y el Hábitat, Número 68, pp. 23 – 29, Julio – Septiembre, 2025, Caracas, Venezuela</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#BolliH1982</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/excursions.html#MillerJB1959</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/ecology.html#LezamaF1989</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/ecology.html#Hoyos1985</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/structural.html#AudemardF2007</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/fields.html#MartinezAR1987</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/geophysics.html#RodriguezI2025</t>
   </si>
 </sst>
 </file>
@@ -47484,13 +47559,13 @@
         <v>4716</v>
       </c>
       <c r="G1281" s="1" t="str">
-        <f t="shared" ref="G1281:G1344" si="41">HYPERLINK(F1281)</f>
+        <f t="shared" ref="G1281:G1345" si="41">HYPERLINK(F1281)</f>
         <v>https://mariantoc.github.io/minerals.html#Ayalaetal2010</v>
       </c>
     </row>
     <row r="1282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1282">
-        <f t="shared" ref="A1282:A1344" si="42">A1281+1</f>
+        <f t="shared" ref="A1282:A1345" si="42">A1281+1</f>
         <v>1281</v>
       </c>
       <c r="B1282" t="s">
@@ -48872,7 +48947,7 @@
       <c r="E1338" t="s">
         <v>4907</v>
       </c>
-      <c r="F1338" s="8" t="s">
+      <c r="F1338" t="s">
         <v>4926</v>
       </c>
       <c r="G1338" s="1" t="str">
@@ -48897,7 +48972,7 @@
       <c r="E1339" t="s">
         <v>4910</v>
       </c>
-      <c r="F1339" s="8" t="s">
+      <c r="F1339" t="s">
         <v>4925</v>
       </c>
       <c r="G1339" s="1" t="str">
@@ -48922,7 +48997,7 @@
       <c r="E1340" t="s">
         <v>4912</v>
       </c>
-      <c r="F1340" s="8" t="s">
+      <c r="F1340" t="s">
         <v>4927</v>
       </c>
       <c r="G1340" s="1" t="str">
@@ -48947,7 +49022,7 @@
       <c r="E1341" t="s">
         <v>4914</v>
       </c>
-      <c r="F1341" s="8" t="s">
+      <c r="F1341" t="s">
         <v>4928</v>
       </c>
       <c r="G1341" s="1" t="str">
@@ -48972,7 +49047,7 @@
       <c r="E1342" t="s">
         <v>4919</v>
       </c>
-      <c r="F1342" s="8" t="s">
+      <c r="F1342" t="s">
         <v>4929</v>
       </c>
       <c r="G1342" s="1" t="str">
@@ -48997,7 +49072,7 @@
       <c r="E1343" t="s">
         <v>4922</v>
       </c>
-      <c r="F1343" s="8" t="s">
+      <c r="F1343" t="s">
         <v>4930</v>
       </c>
       <c r="G1343" s="1" t="str">
@@ -49019,7 +49094,7 @@
       <c r="E1344" t="s">
         <v>4924</v>
       </c>
-      <c r="F1344" s="8" t="s">
+      <c r="F1344" t="s">
         <v>4931</v>
       </c>
       <c r="G1344" s="1" t="str">
@@ -49027,82 +49102,222 @@
         <v>https://mariantoc.github.io/ecology.html#Guatopo1989</v>
       </c>
     </row>
-    <row r="1345" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1345" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1346" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1346" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1347" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1347" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1348" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1348" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1349" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1349" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1350" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1350" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1351" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1351" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1352" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1345" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1345">
+        <f t="shared" si="42"/>
+        <v>1344</v>
+      </c>
+      <c r="B1345" t="s">
+        <v>4932</v>
+      </c>
+      <c r="C1345" t="s">
+        <v>2943</v>
+      </c>
+      <c r="D1345">
+        <v>1982</v>
+      </c>
+      <c r="E1345" t="s">
+        <v>4933</v>
+      </c>
+      <c r="F1345" s="8" t="s">
+        <v>4950</v>
+      </c>
+      <c r="G1345" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#BolliH1982</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1346">
+        <f t="shared" ref="A1346:A1351" si="43">A1345+1</f>
+        <v>1345</v>
+      </c>
+      <c r="B1346" t="s">
+        <v>4934</v>
+      </c>
+      <c r="C1346" t="s">
+        <v>4935</v>
+      </c>
+      <c r="D1346">
+        <v>1959</v>
+      </c>
+      <c r="E1346" t="s">
+        <v>4936</v>
+      </c>
+      <c r="F1346" s="8" t="s">
+        <v>4951</v>
+      </c>
+      <c r="G1346" s="1" t="str">
+        <f t="shared" ref="G1346:G1351" si="44">HYPERLINK(F1346)</f>
+        <v>https://mariantoc.github.io/excursions.html#MillerJB1959</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1347">
+        <f t="shared" si="43"/>
+        <v>1346</v>
+      </c>
+      <c r="B1347" t="s">
+        <v>4937</v>
+      </c>
+      <c r="C1347" t="s">
+        <v>2967</v>
+      </c>
+      <c r="D1347">
+        <v>1989</v>
+      </c>
+      <c r="E1347" t="s">
+        <v>4938</v>
+      </c>
+      <c r="F1347" s="8" t="s">
+        <v>4952</v>
+      </c>
+      <c r="G1347" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/ecology.html#LezamaF1989</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1348">
+        <f t="shared" si="43"/>
+        <v>1347</v>
+      </c>
+      <c r="B1348" t="s">
+        <v>4939</v>
+      </c>
+      <c r="C1348" t="s">
+        <v>4940</v>
+      </c>
+      <c r="D1348">
+        <v>1985</v>
+      </c>
+      <c r="E1348" t="s">
+        <v>4941</v>
+      </c>
+      <c r="F1348" s="8" t="s">
+        <v>4953</v>
+      </c>
+      <c r="G1348" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/ecology.html#Hoyos1985</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1349">
+        <f t="shared" si="43"/>
+        <v>1348</v>
+      </c>
+      <c r="B1349" t="s">
+        <v>4942</v>
+      </c>
+      <c r="C1349" t="s">
+        <v>4943</v>
+      </c>
+      <c r="D1349">
+        <v>1997</v>
+      </c>
+      <c r="E1349" t="s">
+        <v>4944</v>
+      </c>
+      <c r="F1349" s="8" t="s">
+        <v>4954</v>
+      </c>
+      <c r="G1349" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/structural.html#AudemardF2007</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1350">
+        <f t="shared" si="43"/>
+        <v>1349</v>
+      </c>
+      <c r="B1350" t="s">
+        <v>4945</v>
+      </c>
+      <c r="C1350" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D1350">
+        <v>1987</v>
+      </c>
+      <c r="E1350" t="s">
+        <v>4946</v>
+      </c>
+      <c r="F1350" s="8" t="s">
+        <v>4955</v>
+      </c>
+      <c r="G1350" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/fields.html#MartinezAR1987</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1351">
+        <f t="shared" si="43"/>
+        <v>1350</v>
+      </c>
+      <c r="B1351" t="s">
+        <v>4947</v>
+      </c>
+      <c r="C1351" t="s">
+        <v>4948</v>
+      </c>
+      <c r="D1351">
+        <v>2025</v>
+      </c>
+      <c r="E1351" t="s">
+        <v>4949</v>
+      </c>
+      <c r="F1351" s="8" t="s">
+        <v>4956</v>
+      </c>
+      <c r="G1351" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/geophysics.html#RodriguezI2025</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1352" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1353" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1353" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1353" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1354" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1354" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1354" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1355" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1355" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1355" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1356" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1356" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1356" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1357" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1357" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1357" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1358" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1358" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1358" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1359" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1359" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1359" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1360" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1360" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1360" s="7" t="s">
         <v>4315</v>
       </c>

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B9C7C7-6811-4ABC-A98D-1D1366CE4DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7487D634-C1FB-4BFF-805B-10475B18C752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5387" uniqueCount="4957">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5407" uniqueCount="4982">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -15244,6 +15244,81 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/geophysics.html#RodriguezI2025</t>
+  </si>
+  <si>
+    <t>Ruth Agnes Robertson Marietta (mayo 24, 1905 – febrero 17, 1998). El legado de una fotoperiodista estadounidense en Venezuela.</t>
+  </si>
+  <si>
+    <t>Pozo OG-1 (Oficina1): El pozo que cambio la historia de la Cuenca Oriental de Venezuela.</t>
+  </si>
+  <si>
+    <t>Jesús S. Porras y Hernán R. Meneses C.</t>
+  </si>
+  <si>
+    <t>MAYA. Revista de Geociencias, septiembre 2026</t>
+  </si>
+  <si>
+    <t>MAYA, Revista de Geociencias, septiembre 2026</t>
+  </si>
+  <si>
+    <t>Excursión geológica – minera a la región de Bailadores – Guaraque, Distrito Rivas Dávila, Estado Mérida, Venezuela.</t>
+  </si>
+  <si>
+    <t>Moya, E.; Sifontes, R. S.; García, D. E.</t>
+  </si>
+  <si>
+    <t>Memoria del Segundo Congreso Latinoamericano de Geología, Caracas, Venezuela. 11 al 16 de Noviembre de 1973, Tomo I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introducción a los foraminíferos bentónicos. </t>
+  </si>
+  <si>
+    <t>Barun K. Sen Gupta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lower Cretaceous Palynostratigraphy, organic sedimentology and evolution of the Maracaibo Basin, western Venezuela. </t>
+  </si>
+  <si>
+    <t>Omar Colmenares</t>
+  </si>
+  <si>
+    <t>A thesis submitted in the conformity with the requirements for the Degree of Doctor of Philosophy Department of Geology in the University of Toronto, Canada, 1994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un tesoro natural llamado Paria. </t>
+  </si>
+  <si>
+    <t>Juan Carlos Jacome</t>
+  </si>
+  <si>
+    <t>Carta Ecológica de Lagoven S.A., Número 43, Julio – Agosto, 1988</t>
+  </si>
+  <si>
+    <t>Incorporación de la ingeniera Inírida Rodríguez Millán como Miembro Correspondiente Nacional ANIH por el estado Anzoátegui.</t>
+  </si>
+  <si>
+    <t>Academia Nacional de la Ingeniería y el Hábitat, 2025</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#CastroM2026e</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/fields.html#PorrasJSMenesesHR2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/excursions.html#MoyaEetal1973</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#Sen-GuptaBJ1980</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#ColmenaresO1994</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/ecology.html#JacomeJC1988</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#RodriguezI2025</t>
   </si>
 </sst>
 </file>
@@ -49119,7 +49194,7 @@
       <c r="E1345" t="s">
         <v>4933</v>
       </c>
-      <c r="F1345" s="8" t="s">
+      <c r="F1345" t="s">
         <v>4950</v>
       </c>
       <c r="G1345" s="1" t="str">
@@ -49129,7 +49204,7 @@
     </row>
     <row r="1346" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1346">
-        <f t="shared" ref="A1346:A1351" si="43">A1345+1</f>
+        <f t="shared" ref="A1346:A1358" si="43">A1345+1</f>
         <v>1345</v>
       </c>
       <c r="B1346" t="s">
@@ -49144,11 +49219,11 @@
       <c r="E1346" t="s">
         <v>4936</v>
       </c>
-      <c r="F1346" s="8" t="s">
+      <c r="F1346" t="s">
         <v>4951</v>
       </c>
       <c r="G1346" s="1" t="str">
-        <f t="shared" ref="G1346:G1351" si="44">HYPERLINK(F1346)</f>
+        <f t="shared" ref="G1346:G1358" si="44">HYPERLINK(F1346)</f>
         <v>https://mariantoc.github.io/excursions.html#MillerJB1959</v>
       </c>
     </row>
@@ -49169,7 +49244,7 @@
       <c r="E1347" t="s">
         <v>4938</v>
       </c>
-      <c r="F1347" s="8" t="s">
+      <c r="F1347" t="s">
         <v>4952</v>
       </c>
       <c r="G1347" s="1" t="str">
@@ -49194,7 +49269,7 @@
       <c r="E1348" t="s">
         <v>4941</v>
       </c>
-      <c r="F1348" s="8" t="s">
+      <c r="F1348" t="s">
         <v>4953</v>
       </c>
       <c r="G1348" s="1" t="str">
@@ -49219,7 +49294,7 @@
       <c r="E1349" t="s">
         <v>4944</v>
       </c>
-      <c r="F1349" s="8" t="s">
+      <c r="F1349" t="s">
         <v>4954</v>
       </c>
       <c r="G1349" s="1" t="str">
@@ -49244,7 +49319,7 @@
       <c r="E1350" t="s">
         <v>4946</v>
       </c>
-      <c r="F1350" s="8" t="s">
+      <c r="F1350" t="s">
         <v>4955</v>
       </c>
       <c r="G1350" s="1" t="str">
@@ -49269,7 +49344,7 @@
       <c r="E1351" t="s">
         <v>4949</v>
       </c>
-      <c r="F1351" s="8" t="s">
+      <c r="F1351" t="s">
         <v>4956</v>
       </c>
       <c r="G1351" s="1" t="str">
@@ -49278,38 +49353,175 @@
       </c>
     </row>
     <row r="1352" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1352" s="7" t="s">
-        <v>4315</v>
+      <c r="A1352">
+        <f t="shared" si="43"/>
+        <v>1351</v>
+      </c>
+      <c r="B1352" t="s">
+        <v>4957</v>
+      </c>
+      <c r="C1352" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1352">
+        <v>2026</v>
+      </c>
+      <c r="E1352" t="s">
+        <v>4960</v>
+      </c>
+      <c r="F1352" s="8" t="s">
+        <v>4975</v>
+      </c>
+      <c r="G1352" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/biography.html#CastroM2026e</v>
       </c>
     </row>
     <row r="1353" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1353" s="7" t="s">
-        <v>4315</v>
+      <c r="A1353">
+        <f t="shared" si="43"/>
+        <v>1352</v>
+      </c>
+      <c r="B1353" t="s">
+        <v>4958</v>
+      </c>
+      <c r="C1353" t="s">
+        <v>4959</v>
+      </c>
+      <c r="D1353">
+        <v>2026</v>
+      </c>
+      <c r="E1353" t="s">
+        <v>4961</v>
+      </c>
+      <c r="F1353" s="8" t="s">
+        <v>4976</v>
+      </c>
+      <c r="G1353" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/fields.html#PorrasJSMenesesHR2026</v>
       </c>
     </row>
     <row r="1354" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1354" s="7" t="s">
-        <v>4315</v>
+      <c r="A1354">
+        <f t="shared" si="43"/>
+        <v>1353</v>
+      </c>
+      <c r="B1354" t="s">
+        <v>4962</v>
+      </c>
+      <c r="C1354" t="s">
+        <v>4963</v>
+      </c>
+      <c r="D1354">
+        <v>1973</v>
+      </c>
+      <c r="E1354" t="s">
+        <v>4964</v>
+      </c>
+      <c r="F1354" s="8" t="s">
+        <v>4977</v>
+      </c>
+      <c r="G1354" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/excursions.html#MoyaEetal1973</v>
       </c>
     </row>
     <row r="1355" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1355" s="7" t="s">
-        <v>4315</v>
+      <c r="A1355">
+        <f t="shared" si="43"/>
+        <v>1354</v>
+      </c>
+      <c r="B1355" t="s">
+        <v>4965</v>
+      </c>
+      <c r="C1355" t="s">
+        <v>4966</v>
+      </c>
+      <c r="D1355">
+        <v>1980</v>
+      </c>
+      <c r="E1355" t="s">
+        <v>4834</v>
+      </c>
+      <c r="F1355" s="8" t="s">
+        <v>4978</v>
+      </c>
+      <c r="G1355" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#Sen-GuptaBJ1980</v>
       </c>
     </row>
     <row r="1356" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1356" s="7" t="s">
-        <v>4315</v>
+      <c r="A1356">
+        <f t="shared" si="43"/>
+        <v>1355</v>
+      </c>
+      <c r="B1356" t="s">
+        <v>4967</v>
+      </c>
+      <c r="C1356" t="s">
+        <v>4968</v>
+      </c>
+      <c r="D1356">
+        <v>1994</v>
+      </c>
+      <c r="E1356" t="s">
+        <v>4969</v>
+      </c>
+      <c r="F1356" s="8" t="s">
+        <v>4979</v>
+      </c>
+      <c r="G1356" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#ColmenaresO1994</v>
       </c>
     </row>
     <row r="1357" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1357" s="7" t="s">
-        <v>4315</v>
+      <c r="A1357">
+        <f t="shared" si="43"/>
+        <v>1356</v>
+      </c>
+      <c r="B1357" t="s">
+        <v>4970</v>
+      </c>
+      <c r="C1357" t="s">
+        <v>4971</v>
+      </c>
+      <c r="D1357">
+        <v>1988</v>
+      </c>
+      <c r="E1357" t="s">
+        <v>4972</v>
+      </c>
+      <c r="F1357" s="8" t="s">
+        <v>4980</v>
+      </c>
+      <c r="G1357" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/ecology.html#JacomeJC1988</v>
       </c>
     </row>
     <row r="1358" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1358" s="7" t="s">
-        <v>4315</v>
+      <c r="A1358">
+        <f t="shared" si="43"/>
+        <v>1357</v>
+      </c>
+      <c r="B1358" t="s">
+        <v>4973</v>
+      </c>
+      <c r="D1358">
+        <v>2025</v>
+      </c>
+      <c r="E1358" t="s">
+        <v>4974</v>
+      </c>
+      <c r="F1358" s="8" t="s">
+        <v>4981</v>
+      </c>
+      <c r="G1358" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/biography.html#RodriguezI2025</v>
       </c>
     </row>
     <row r="1359" spans="1:7" x14ac:dyDescent="0.3">

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7487D634-C1FB-4BFF-805B-10475B18C752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DAEF474-F08A-4142-B949-03767231E3F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5407" uniqueCount="4982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5428" uniqueCount="5007">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -15319,6 +15319,81 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/biography.html#RodriguezI2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biostratigraphy. </t>
+  </si>
+  <si>
+    <t>J. Wyatt Durham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A field guide to Cretaceous facies and sequence stratigraphy of northeastern Venezuela. </t>
+  </si>
+  <si>
+    <t>Kauffman E. G.; Johson, C. C.; Villamil, T.</t>
+  </si>
+  <si>
+    <t>Prepared for INTEVEP, 1994</t>
+  </si>
+  <si>
+    <t>Geologic structure of a part of the Barinas Mountain Front, Venezuelan Andes.</t>
+  </si>
+  <si>
+    <t>Geological Society of America, Bulletin, March 1969</t>
+  </si>
+  <si>
+    <t>Sobre la existencia de sedimentos marinos no metamorfizados del Neocomiense en el noreste del estado Guárico, Venezuela septentrional. Implicaciones paleogeográficas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beck, C. M.; Furrer, M. A. </t>
+  </si>
+  <si>
+    <t>V Congreso Geológico Venezolano, Caracas, Noviembre 1977</t>
+  </si>
+  <si>
+    <t>Imagen y huella de Clemente González de Juana.</t>
+  </si>
+  <si>
+    <t>Publicación de Intevep S.A. Centro de Investigación y Apoyo Tecnológico de Petróleos de Venezuela, Caracas, 1990</t>
+  </si>
+  <si>
+    <t>Aplicaciones de los métodos sísmicos en la exploración del carbón.</t>
+  </si>
+  <si>
+    <t>José Regueiro</t>
+  </si>
+  <si>
+    <t>Memorias de las Primeras Jornadas Geológicas de CarboZulia, Carbones del Zulia C.A., Maracaibo, 1983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parque Nacional Aguaro – Guariquito. Importante refugio para la fauna llanera. </t>
+  </si>
+  <si>
+    <t>Elvira Sanz</t>
+  </si>
+  <si>
+    <t>Carta Ecológica Lagoven S.A., Número 65, Octubre – Diciembre, 1990</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#DurhamJW1982</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/excursions.html#KauffmanEetal1994</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/structural.html#SchubertC1969</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#BeckCMFurrerMA1977</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#MartinezA1990</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/geophysics.html#RegueiroJ1983</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/ecology.html#SanzE1990</t>
   </si>
 </sst>
 </file>
@@ -49204,7 +49279,7 @@
     </row>
     <row r="1346" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1346">
-        <f t="shared" ref="A1346:A1358" si="43">A1345+1</f>
+        <f t="shared" ref="A1346:A1365" si="43">A1345+1</f>
         <v>1345</v>
       </c>
       <c r="B1346" t="s">
@@ -49223,7 +49298,7 @@
         <v>4951</v>
       </c>
       <c r="G1346" s="1" t="str">
-        <f t="shared" ref="G1346:G1358" si="44">HYPERLINK(F1346)</f>
+        <f t="shared" ref="G1346:G1365" si="44">HYPERLINK(F1346)</f>
         <v>https://mariantoc.github.io/excursions.html#MillerJB1959</v>
       </c>
     </row>
@@ -49369,7 +49444,7 @@
       <c r="E1352" t="s">
         <v>4960</v>
       </c>
-      <c r="F1352" s="8" t="s">
+      <c r="F1352" t="s">
         <v>4975</v>
       </c>
       <c r="G1352" s="1" t="str">
@@ -49394,7 +49469,7 @@
       <c r="E1353" t="s">
         <v>4961</v>
       </c>
-      <c r="F1353" s="8" t="s">
+      <c r="F1353" t="s">
         <v>4976</v>
       </c>
       <c r="G1353" s="1" t="str">
@@ -49419,7 +49494,7 @@
       <c r="E1354" t="s">
         <v>4964</v>
       </c>
-      <c r="F1354" s="8" t="s">
+      <c r="F1354" t="s">
         <v>4977</v>
       </c>
       <c r="G1354" s="1" t="str">
@@ -49444,7 +49519,7 @@
       <c r="E1355" t="s">
         <v>4834</v>
       </c>
-      <c r="F1355" s="8" t="s">
+      <c r="F1355" t="s">
         <v>4978</v>
       </c>
       <c r="G1355" s="1" t="str">
@@ -49469,7 +49544,7 @@
       <c r="E1356" t="s">
         <v>4969</v>
       </c>
-      <c r="F1356" s="8" t="s">
+      <c r="F1356" t="s">
         <v>4979</v>
       </c>
       <c r="G1356" s="1" t="str">
@@ -49494,7 +49569,7 @@
       <c r="E1357" t="s">
         <v>4972</v>
       </c>
-      <c r="F1357" s="8" t="s">
+      <c r="F1357" t="s">
         <v>4980</v>
       </c>
       <c r="G1357" s="1" t="str">
@@ -49516,7 +49591,7 @@
       <c r="E1358" t="s">
         <v>4974</v>
       </c>
-      <c r="F1358" s="8" t="s">
+      <c r="F1358" t="s">
         <v>4981</v>
       </c>
       <c r="G1358" s="1" t="str">
@@ -49525,91 +49600,231 @@
       </c>
     </row>
     <row r="1359" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1359" s="7" t="s">
-        <v>4315</v>
+      <c r="A1359">
+        <f t="shared" si="43"/>
+        <v>1358</v>
+      </c>
+      <c r="B1359" t="s">
+        <v>4982</v>
+      </c>
+      <c r="C1359" t="s">
+        <v>4983</v>
+      </c>
+      <c r="D1359">
+        <v>1982</v>
+      </c>
+      <c r="E1359" t="s">
+        <v>4933</v>
+      </c>
+      <c r="F1359" s="8" t="s">
+        <v>5000</v>
+      </c>
+      <c r="G1359" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#DurhamJW1982</v>
       </c>
     </row>
     <row r="1360" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1360" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1361" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1361" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1362" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1362" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1363" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1363" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1364" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1364" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1365" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1365" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1366" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="A1360">
+        <f t="shared" si="43"/>
+        <v>1359</v>
+      </c>
+      <c r="B1360" t="s">
+        <v>4984</v>
+      </c>
+      <c r="C1360" t="s">
+        <v>4985</v>
+      </c>
+      <c r="D1360">
+        <v>1994</v>
+      </c>
+      <c r="E1360" t="s">
+        <v>4986</v>
+      </c>
+      <c r="F1360" s="8" t="s">
+        <v>5001</v>
+      </c>
+      <c r="G1360" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/excursions.html#KauffmanEetal1994</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1361">
+        <f t="shared" si="43"/>
+        <v>1360</v>
+      </c>
+      <c r="B1361" t="s">
+        <v>4987</v>
+      </c>
+      <c r="C1361" t="s">
+        <v>325</v>
+      </c>
+      <c r="D1361">
+        <v>1969</v>
+      </c>
+      <c r="E1361" t="s">
+        <v>4988</v>
+      </c>
+      <c r="F1361" s="8" t="s">
+        <v>5002</v>
+      </c>
+      <c r="G1361" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/structural.html#SchubertC1969</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1362">
+        <f t="shared" si="43"/>
+        <v>1361</v>
+      </c>
+      <c r="B1362" t="s">
+        <v>4989</v>
+      </c>
+      <c r="C1362" t="s">
+        <v>4990</v>
+      </c>
+      <c r="D1362">
+        <v>1977</v>
+      </c>
+      <c r="E1362" t="s">
+        <v>4991</v>
+      </c>
+      <c r="F1362" s="8" t="s">
+        <v>5003</v>
+      </c>
+      <c r="G1362" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#BeckCMFurrerMA1977</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1363">
+        <f t="shared" si="43"/>
+        <v>1362</v>
+      </c>
+      <c r="B1363" t="s">
+        <v>4992</v>
+      </c>
+      <c r="C1363" t="s">
+        <v>1590</v>
+      </c>
+      <c r="D1363">
+        <v>1990</v>
+      </c>
+      <c r="E1363" t="s">
+        <v>4993</v>
+      </c>
+      <c r="F1363" s="8" t="s">
+        <v>5004</v>
+      </c>
+      <c r="G1363" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/biography.html#MartinezA1990</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1364">
+        <f t="shared" si="43"/>
+        <v>1363</v>
+      </c>
+      <c r="B1364" t="s">
+        <v>4994</v>
+      </c>
+      <c r="C1364" t="s">
+        <v>4995</v>
+      </c>
+      <c r="D1364">
+        <v>1983</v>
+      </c>
+      <c r="E1364" t="s">
+        <v>4996</v>
+      </c>
+      <c r="F1364" s="8" t="s">
+        <v>5005</v>
+      </c>
+      <c r="G1364" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/geophysics.html#RegueiroJ1983</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1365">
+        <f t="shared" si="43"/>
+        <v>1364</v>
+      </c>
+      <c r="B1365" t="s">
+        <v>4997</v>
+      </c>
+      <c r="C1365" t="s">
+        <v>4998</v>
+      </c>
+      <c r="D1365">
+        <v>1990</v>
+      </c>
+      <c r="E1365" t="s">
+        <v>4999</v>
+      </c>
+      <c r="F1365" s="8" t="s">
+        <v>5006</v>
+      </c>
+      <c r="G1365" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/ecology.html#SanzE1990</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1366" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1367" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1367" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1367" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1368" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1368" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1368" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1369" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1369" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1369" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1370" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1370" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1370" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1371" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1371" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1371" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1372" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1372" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1372" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1373" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1373" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1373" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1374" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1374" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1374" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1375" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1375" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1375" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1376" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1376" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1376" s="7" t="s">
         <v>4315</v>
       </c>

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DAEF474-F08A-4142-B949-03767231E3F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ADE59E2-1DB9-4764-9D47-FF7F55593AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5428" uniqueCount="5007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5505" uniqueCount="5032">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -15394,6 +15394,81 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/ecology.html#SanzE1990</t>
+  </si>
+  <si>
+    <t>Notes on Post - Paleozoic Ostracoda.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F. P. C. M. Morkhoven </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materias primas en relación con la industria del hierro en Venezuela. </t>
+  </si>
+  <si>
+    <t>Cecilia Martín de Bellizzia y Alirio Bellizzia</t>
+  </si>
+  <si>
+    <t>Boletín de Geología, Ministerio de Energía y Minas, Dirección de Geología, Vo. III, No. 7, Enero – Julio, 1953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidencias históricas de actividad sismotectónica y manifestaciones de inestabilidad geológica en el Alto de Pedernales, entre Venezuela y Trinidad. </t>
+  </si>
+  <si>
+    <t>José Antonio Rodríguez; Franck Audemard; André Singer; Carlos Beltrán</t>
+  </si>
+  <si>
+    <t>3rd. Geological Conference of the Geological Society of Trinidad and Tobago, 1995</t>
+  </si>
+  <si>
+    <t>Gestión de la información post-sísmica del 24 de junio de 2026 en Venezuela.</t>
+  </si>
+  <si>
+    <t>MAYA. Revista de Geociencias, Septiembre 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Studies on Cretaceous acid- insoluble microfossils in western Venezuela. </t>
+  </si>
+  <si>
+    <t>John W. Funkhouser</t>
+  </si>
+  <si>
+    <t>Creole Petroleum Corporation, 1960</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venezuela y la nueva tectónica global. </t>
+  </si>
+  <si>
+    <t>Acta Científica Venezolana, Número 21, pp. 13 – 16, 1970</t>
+  </si>
+  <si>
+    <t>Geological synthesis of the Orinoco Oil Belt, eastern Venezuela.</t>
+  </si>
+  <si>
+    <t>Andreína Isea</t>
+  </si>
+  <si>
+    <t>Journal of Petroleum Geology, Vol. 10, No. 2, pp. 135 – 148, 1987</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#MorkhovenFPCM1982</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/minerals.html#MartinCABellizia1953</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/structural.html#RodriguezJAetal1995</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#RodriguezJA2026c</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#FunkhouserJW1960</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/structural.html#Schubert,C1970</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/fields.html#IseaA1987</t>
   </si>
 </sst>
 </file>
@@ -15818,7 +15893,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B496A77-4B74-49B4-B08F-A7274E320005}">
-  <dimension ref="A1:H1379"/>
+  <dimension ref="A1:H1435"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="66.5546875" customWidth="1"/>
@@ -49279,7 +49354,7 @@
     </row>
     <row r="1346" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1346">
-        <f t="shared" ref="A1346:A1365" si="43">A1345+1</f>
+        <f t="shared" ref="A1346:A1372" si="43">A1345+1</f>
         <v>1345</v>
       </c>
       <c r="B1346" t="s">
@@ -49298,7 +49373,7 @@
         <v>4951</v>
       </c>
       <c r="G1346" s="1" t="str">
-        <f t="shared" ref="G1346:G1365" si="44">HYPERLINK(F1346)</f>
+        <f t="shared" ref="G1346:G1372" si="44">HYPERLINK(F1346)</f>
         <v>https://mariantoc.github.io/excursions.html#MillerJB1959</v>
       </c>
     </row>
@@ -49616,7 +49691,7 @@
       <c r="E1359" t="s">
         <v>4933</v>
       </c>
-      <c r="F1359" s="8" t="s">
+      <c r="F1359" t="s">
         <v>5000</v>
       </c>
       <c r="G1359" s="1" t="str">
@@ -49641,7 +49716,7 @@
       <c r="E1360" t="s">
         <v>4986</v>
       </c>
-      <c r="F1360" s="8" t="s">
+      <c r="F1360" t="s">
         <v>5001</v>
       </c>
       <c r="G1360" s="1" t="str">
@@ -49666,7 +49741,7 @@
       <c r="E1361" t="s">
         <v>4988</v>
       </c>
-      <c r="F1361" s="8" t="s">
+      <c r="F1361" t="s">
         <v>5002</v>
       </c>
       <c r="G1361" s="1" t="str">
@@ -49691,7 +49766,7 @@
       <c r="E1362" t="s">
         <v>4991</v>
       </c>
-      <c r="F1362" s="8" t="s">
+      <c r="F1362" t="s">
         <v>5003</v>
       </c>
       <c r="G1362" s="1" t="str">
@@ -49716,7 +49791,7 @@
       <c r="E1363" t="s">
         <v>4993</v>
       </c>
-      <c r="F1363" s="8" t="s">
+      <c r="F1363" t="s">
         <v>5004</v>
       </c>
       <c r="G1363" s="1" t="str">
@@ -49741,7 +49816,7 @@
       <c r="E1364" t="s">
         <v>4996</v>
       </c>
-      <c r="F1364" s="8" t="s">
+      <c r="F1364" t="s">
         <v>5005</v>
       </c>
       <c r="G1364" s="1" t="str">
@@ -49766,7 +49841,7 @@
       <c r="E1365" t="s">
         <v>4999</v>
       </c>
-      <c r="F1365" s="8" t="s">
+      <c r="F1365" t="s">
         <v>5006</v>
       </c>
       <c r="G1365" s="1" t="str">
@@ -49775,38 +49850,178 @@
       </c>
     </row>
     <row r="1366" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1366" s="7" t="s">
-        <v>4315</v>
+      <c r="A1366">
+        <f t="shared" si="43"/>
+        <v>1365</v>
+      </c>
+      <c r="B1366" t="s">
+        <v>5007</v>
+      </c>
+      <c r="C1366" t="s">
+        <v>5008</v>
+      </c>
+      <c r="D1366">
+        <v>1982</v>
+      </c>
+      <c r="E1366" t="s">
+        <v>4933</v>
+      </c>
+      <c r="F1366" s="8" t="s">
+        <v>5025</v>
+      </c>
+      <c r="G1366" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#MorkhovenFPCM1982</v>
       </c>
     </row>
     <row r="1367" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1367" s="7" t="s">
-        <v>4315</v>
+      <c r="A1367">
+        <f t="shared" si="43"/>
+        <v>1366</v>
+      </c>
+      <c r="B1367" t="s">
+        <v>5009</v>
+      </c>
+      <c r="C1367" t="s">
+        <v>5010</v>
+      </c>
+      <c r="D1367">
+        <v>1953</v>
+      </c>
+      <c r="E1367" t="s">
+        <v>5011</v>
+      </c>
+      <c r="F1367" s="8" t="s">
+        <v>5026</v>
+      </c>
+      <c r="G1367" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/minerals.html#MartinCABellizia1953</v>
       </c>
     </row>
     <row r="1368" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1368" s="7" t="s">
-        <v>4315</v>
+      <c r="A1368">
+        <f t="shared" si="43"/>
+        <v>1367</v>
+      </c>
+      <c r="B1368" t="s">
+        <v>5012</v>
+      </c>
+      <c r="C1368" t="s">
+        <v>5013</v>
+      </c>
+      <c r="D1368">
+        <v>1995</v>
+      </c>
+      <c r="E1368" t="s">
+        <v>5014</v>
+      </c>
+      <c r="F1368" s="8" t="s">
+        <v>5027</v>
+      </c>
+      <c r="G1368" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/structural.html#RodriguezJAetal1995</v>
       </c>
     </row>
     <row r="1369" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1369" s="7" t="s">
-        <v>4315</v>
+      <c r="A1369">
+        <f t="shared" si="43"/>
+        <v>1368</v>
+      </c>
+      <c r="B1369" t="s">
+        <v>5015</v>
+      </c>
+      <c r="C1369" t="s">
+        <v>341</v>
+      </c>
+      <c r="D1369">
+        <v>2026</v>
+      </c>
+      <c r="E1369" t="s">
+        <v>5016</v>
+      </c>
+      <c r="F1369" s="8" t="s">
+        <v>5028</v>
+      </c>
+      <c r="G1369" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/biography.html#RodriguezJA2026c</v>
       </c>
     </row>
     <row r="1370" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1370" s="7" t="s">
-        <v>4315</v>
+      <c r="A1370">
+        <f t="shared" si="43"/>
+        <v>1369</v>
+      </c>
+      <c r="B1370" t="s">
+        <v>5017</v>
+      </c>
+      <c r="C1370" t="s">
+        <v>5018</v>
+      </c>
+      <c r="D1370">
+        <v>1960</v>
+      </c>
+      <c r="E1370" t="s">
+        <v>5019</v>
+      </c>
+      <c r="F1370" s="8" t="s">
+        <v>5029</v>
+      </c>
+      <c r="G1370" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#FunkhouserJW1960</v>
       </c>
     </row>
     <row r="1371" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1371" s="7" t="s">
-        <v>4315</v>
+      <c r="A1371">
+        <f t="shared" si="43"/>
+        <v>1370</v>
+      </c>
+      <c r="B1371" t="s">
+        <v>5020</v>
+      </c>
+      <c r="C1371" t="s">
+        <v>325</v>
+      </c>
+      <c r="D1371">
+        <v>1970</v>
+      </c>
+      <c r="E1371" t="s">
+        <v>5021</v>
+      </c>
+      <c r="F1371" s="8" t="s">
+        <v>5030</v>
+      </c>
+      <c r="G1371" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/structural.html#Schubert,C1970</v>
       </c>
     </row>
     <row r="1372" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1372" s="7" t="s">
-        <v>4315</v>
+      <c r="A1372">
+        <f t="shared" si="43"/>
+        <v>1371</v>
+      </c>
+      <c r="B1372" t="s">
+        <v>5022</v>
+      </c>
+      <c r="C1372" t="s">
+        <v>5023</v>
+      </c>
+      <c r="D1372">
+        <v>1987</v>
+      </c>
+      <c r="E1372" t="s">
+        <v>5024</v>
+      </c>
+      <c r="F1372" s="8" t="s">
+        <v>5031</v>
+      </c>
+      <c r="G1372" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/fields.html#IseaA1987</v>
       </c>
     </row>
     <row r="1373" spans="1:7" x14ac:dyDescent="0.3">
@@ -49841,6 +50056,286 @@
     </row>
     <row r="1379" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1379" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1380" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1380" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1381" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1381" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1382" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1382" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1383" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1383" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1384" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1384" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1385" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1385" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1386" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1386" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1387" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1387" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1388" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1388" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1389" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1389" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1390" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1390" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1391" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1391" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1392" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1392" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1393" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1393" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1394" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1394" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1395" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1395" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1396" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1396" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1397" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1397" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1398" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1398" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1399" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1399" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1400" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1400" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1401" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1401" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1402" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1402" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1403" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1403" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1404" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1404" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1405" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1405" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1406" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1406" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1407" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1407" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1408" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1408" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1409" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1409" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1410" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1410" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1411" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1411" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1412" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1412" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1413" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1413" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1414" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1414" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1415" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1415" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1416" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1416" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1417" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1417" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1418" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1418" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1419" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1419" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1420" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1420" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1421" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1421" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1422" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1422" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1423" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1423" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1424" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1424" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1425" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1425" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1426" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1426" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1427" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1427" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1428" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1428" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1429" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1429" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1430" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1430" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1431" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1431" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1432" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1432" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1433" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1433" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1434" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1434" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1435" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1435" s="7" t="s">
         <v>4315</v>
       </c>
     </row>

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ADE59E2-1DB9-4764-9D47-FF7F55593AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87A221C2-A241-451D-861F-9D74E5F5442D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5505" uniqueCount="5032">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5526" uniqueCount="5054">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -15469,6 +15469,72 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/fields.html#IseaA1987</t>
+  </si>
+  <si>
+    <t>Descubriendo el Maravilloso Universo de las Ciencias de la Tierra.</t>
+  </si>
+  <si>
+    <t>Charla introducción a la asignatura Bioestratigrafía, 1998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Técnicas para la recolección, preparación y estudio de icnofósiles continentales. </t>
+  </si>
+  <si>
+    <t>José H. Laza</t>
+  </si>
+  <si>
+    <t>Revista del Museo de La Plata, Volumen 9, Número 2, pp. 177 – 211, 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breve novedad para el estudio del terremoto de 1900 en Caracas, Coll y Unamuno. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La geología en el deporte: Materiales, superficies y entorno natural. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sismos del 2025 en la Costa Oriental del Lago de Maracaibo: Análisis de la secuencia sísmica, vulnerabilidad de las edificaciones educativas y guía esencial de prevención. </t>
+  </si>
+  <si>
+    <t>Boletín de la Academia Nacional de la Ingeniería y el Hábitat, Número 69, Octubre – Diciembre, 2025, Caracas, Venezuela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bibliografía de artículos concernientes a Venezuela, Colombia y Trinidad publicados en los Boletines de la AAPG entre 1922 y 1958. </t>
+  </si>
+  <si>
+    <t>Douglas J.</t>
+  </si>
+  <si>
+    <t>Boletín Informativo de la Asociación Venezolana de Geología, Minería y Petróleo, Volumen 1, Número 3, Septiembre 1958</t>
+  </si>
+  <si>
+    <t>Informe geológico sobre la región carbonífera de los estados Aragua y Guárico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pérez Mena, R. L.; Von Der Osten, E. </t>
+  </si>
+  <si>
+    <t>Ministerio de Minas e Hidrocarburos, Dirección de Geología, Boletín de Geología, Volumen III, Número 7, Enero – Julio, 1953</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#CastroM1998a</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#LazaJH2024</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#RodriguezJA2026d</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/topics.html#PorrasJS2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#MarinoiN2025</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#DouglasJ1958</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/minerals.html#PerezRVonderOstenE1953</t>
   </si>
 </sst>
 </file>
@@ -49354,7 +49420,7 @@
     </row>
     <row r="1346" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1346">
-        <f t="shared" ref="A1346:A1372" si="43">A1345+1</f>
+        <f t="shared" ref="A1346:A1379" si="43">A1345+1</f>
         <v>1345</v>
       </c>
       <c r="B1346" t="s">
@@ -49373,7 +49439,7 @@
         <v>4951</v>
       </c>
       <c r="G1346" s="1" t="str">
-        <f t="shared" ref="G1346:G1372" si="44">HYPERLINK(F1346)</f>
+        <f t="shared" ref="G1346:G1379" si="44">HYPERLINK(F1346)</f>
         <v>https://mariantoc.github.io/excursions.html#MillerJB1959</v>
       </c>
     </row>
@@ -49866,7 +49932,7 @@
       <c r="E1366" t="s">
         <v>4933</v>
       </c>
-      <c r="F1366" s="8" t="s">
+      <c r="F1366" t="s">
         <v>5025</v>
       </c>
       <c r="G1366" s="1" t="str">
@@ -49891,7 +49957,7 @@
       <c r="E1367" t="s">
         <v>5011</v>
       </c>
-      <c r="F1367" s="8" t="s">
+      <c r="F1367" t="s">
         <v>5026</v>
       </c>
       <c r="G1367" s="1" t="str">
@@ -49916,7 +49982,7 @@
       <c r="E1368" t="s">
         <v>5014</v>
       </c>
-      <c r="F1368" s="8" t="s">
+      <c r="F1368" t="s">
         <v>5027</v>
       </c>
       <c r="G1368" s="1" t="str">
@@ -49941,7 +50007,7 @@
       <c r="E1369" t="s">
         <v>5016</v>
       </c>
-      <c r="F1369" s="8" t="s">
+      <c r="F1369" t="s">
         <v>5028</v>
       </c>
       <c r="G1369" s="1" t="str">
@@ -49966,7 +50032,7 @@
       <c r="E1370" t="s">
         <v>5019</v>
       </c>
-      <c r="F1370" s="8" t="s">
+      <c r="F1370" t="s">
         <v>5029</v>
       </c>
       <c r="G1370" s="1" t="str">
@@ -49991,7 +50057,7 @@
       <c r="E1371" t="s">
         <v>5021</v>
       </c>
-      <c r="F1371" s="8" t="s">
+      <c r="F1371" t="s">
         <v>5030</v>
       </c>
       <c r="G1371" s="1" t="str">
@@ -50016,7 +50082,7 @@
       <c r="E1372" t="s">
         <v>5024</v>
       </c>
-      <c r="F1372" s="8" t="s">
+      <c r="F1372" t="s">
         <v>5031</v>
       </c>
       <c r="G1372" s="1" t="str">
@@ -50025,101 +50091,241 @@
       </c>
     </row>
     <row r="1373" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1373" s="7" t="s">
-        <v>4315</v>
+      <c r="A1373">
+        <f t="shared" si="43"/>
+        <v>1372</v>
+      </c>
+      <c r="B1373" t="s">
+        <v>5032</v>
+      </c>
+      <c r="C1373" t="s">
+        <v>2880</v>
+      </c>
+      <c r="D1373">
+        <v>1998</v>
+      </c>
+      <c r="E1373" t="s">
+        <v>5033</v>
+      </c>
+      <c r="F1373" s="8" t="s">
+        <v>5047</v>
+      </c>
+      <c r="G1373" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#CastroM1998a</v>
       </c>
     </row>
     <row r="1374" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1374" s="7" t="s">
-        <v>4315</v>
+      <c r="A1374">
+        <f t="shared" si="43"/>
+        <v>1373</v>
+      </c>
+      <c r="B1374" t="s">
+        <v>5034</v>
+      </c>
+      <c r="C1374" t="s">
+        <v>5035</v>
+      </c>
+      <c r="D1374">
+        <v>2024</v>
+      </c>
+      <c r="E1374" t="s">
+        <v>5036</v>
+      </c>
+      <c r="F1374" s="8" t="s">
+        <v>5048</v>
+      </c>
+      <c r="G1374" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#LazaJH2024</v>
       </c>
     </row>
     <row r="1375" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1375" s="7" t="s">
-        <v>4315</v>
+      <c r="A1375">
+        <f t="shared" si="43"/>
+        <v>1374</v>
+      </c>
+      <c r="B1375" t="s">
+        <v>5037</v>
+      </c>
+      <c r="C1375" t="s">
+        <v>341</v>
+      </c>
+      <c r="D1375">
+        <v>2026</v>
+      </c>
+      <c r="E1375" t="s">
+        <v>5016</v>
+      </c>
+      <c r="F1375" s="8" t="s">
+        <v>5049</v>
+      </c>
+      <c r="G1375" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/biography.html#RodriguezJA2026d</v>
       </c>
     </row>
     <row r="1376" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1376" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1377" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1377" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1378" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1378" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1379" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1379" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1380" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="A1376">
+        <f t="shared" si="43"/>
+        <v>1375</v>
+      </c>
+      <c r="B1376" t="s">
+        <v>5038</v>
+      </c>
+      <c r="C1376" t="s">
+        <v>4676</v>
+      </c>
+      <c r="D1376">
+        <v>2026</v>
+      </c>
+      <c r="E1376" t="s">
+        <v>4738</v>
+      </c>
+      <c r="F1376" s="8" t="s">
+        <v>5050</v>
+      </c>
+      <c r="G1376" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/topics.html#PorrasJS2026</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1377">
+        <f t="shared" si="43"/>
+        <v>1376</v>
+      </c>
+      <c r="B1377" t="s">
+        <v>5039</v>
+      </c>
+      <c r="C1377" t="s">
+        <v>297</v>
+      </c>
+      <c r="D1377">
+        <v>2025</v>
+      </c>
+      <c r="E1377" t="s">
+        <v>5040</v>
+      </c>
+      <c r="F1377" s="8" t="s">
+        <v>5051</v>
+      </c>
+      <c r="G1377" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/biography.html#MarinoiN2025</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1378">
+        <f t="shared" si="43"/>
+        <v>1377</v>
+      </c>
+      <c r="B1378" t="s">
+        <v>5041</v>
+      </c>
+      <c r="C1378" t="s">
+        <v>5042</v>
+      </c>
+      <c r="D1378">
+        <v>1958</v>
+      </c>
+      <c r="E1378" t="s">
+        <v>5043</v>
+      </c>
+      <c r="F1378" s="8" t="s">
+        <v>5052</v>
+      </c>
+      <c r="G1378" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/biography.html#DouglasJ1958</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1379">
+        <f t="shared" si="43"/>
+        <v>1378</v>
+      </c>
+      <c r="B1379" t="s">
+        <v>5044</v>
+      </c>
+      <c r="C1379" t="s">
+        <v>5045</v>
+      </c>
+      <c r="D1379">
+        <v>1953</v>
+      </c>
+      <c r="E1379" t="s">
+        <v>5046</v>
+      </c>
+      <c r="F1379" s="8" t="s">
+        <v>5053</v>
+      </c>
+      <c r="G1379" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/minerals.html#PerezRVonderOstenE1953</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1380" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1381" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1381" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1381" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1382" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1382" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1382" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1383" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1383" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1383" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1384" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1384" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1384" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1385" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1385" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1385" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1386" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1386" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1386" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1387" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1387" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1387" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1388" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1388" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1388" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1389" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1389" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1389" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1390" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1390" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1390" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1391" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1391" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1391" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1392" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1392" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1392" s="7" t="s">
         <v>4315</v>
       </c>

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87A221C2-A241-451D-861F-9D74E5F5442D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918755D0-25FE-41BC-956B-9ADB073D78EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5526" uniqueCount="5054">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5545" uniqueCount="5077">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -15535,6 +15535,75 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/minerals.html#PerezRVonderOstenE1953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrón estructural de las vetas y zonas de cizalla auríferas del Distrito Minero Las Claritas, kilómetro 88, estado Bolívar, Venezuela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moreno A., C. C.; Quintero F., K. L.; Gallardo, E. </t>
+  </si>
+  <si>
+    <t>Boletín de Geología, Volumen XXI, Número 34, Instituto Nacional de Geología y Minería (INGEOMIN), 2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descubriendo el potencial no convencional de la Formación La Luna en Venezuela. Lecciones del desarrollo sale de Estados Unidos y Argentina para Venezuela. </t>
+  </si>
+  <si>
+    <t>Jesús S. Porras, 2026</t>
+  </si>
+  <si>
+    <t>Petroleum. Septiembre 28, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEOS. Revista Venezolana de Ciencias de La Tierra. Indice general de los números 1 (1959, primer ejemplar publicado) al 47 (2015, último ejemplar publicado). </t>
+  </si>
+  <si>
+    <t>Listado preparado por el profesor Dr. Franco Urbani Patat, Agosto 2017</t>
+  </si>
+  <si>
+    <t>Principales grupos fósiles. Introducción.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depósitos de bauxitas en el Escudo de Guayana, Venezuela. Potencialidades y ventajas comparativas. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vicente Mendoza; Antonio Bronjanigo; Allan Reyes y Héctor A. Márquez S. </t>
+  </si>
+  <si>
+    <t>Maya. Revista de Geociencias, Suplemento Especial, Abril 2026, pp. 64 -81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selected isotopic age determinations on Trans-Amazonian granitoids. </t>
+  </si>
+  <si>
+    <t>In: The geology of the Guiana Shield. A. K. Gibbs and C. N. Barrow, Oxford Monographs on geology and geophysics, No. 22, 1993</t>
+  </si>
+  <si>
+    <t>La Universidad de Oriente (UDO) crea la cátedra “Faja Petrolífera del Orinoco” en Venezuela.</t>
+  </si>
+  <si>
+    <t>Energy Magazine. Energía que conecta el mañana, Agosto – Septiembre, 2026. Edición Especial</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/minerals.html#MorenoACCetal2015</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/fields.html#PorrasJS2026a</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#UrbaniF2017</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#CastroM1998b</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/minerals.html#MendozaVetal2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/igneous.html#AgeGranitoides1993</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#UDO2026</t>
   </si>
 </sst>
 </file>
@@ -49420,7 +49489,7 @@
     </row>
     <row r="1346" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1346">
-        <f t="shared" ref="A1346:A1379" si="43">A1345+1</f>
+        <f t="shared" ref="A1346:A1386" si="43">A1345+1</f>
         <v>1345</v>
       </c>
       <c r="B1346" t="s">
@@ -49439,7 +49508,7 @@
         <v>4951</v>
       </c>
       <c r="G1346" s="1" t="str">
-        <f t="shared" ref="G1346:G1379" si="44">HYPERLINK(F1346)</f>
+        <f t="shared" ref="G1346:G1386" si="44">HYPERLINK(F1346)</f>
         <v>https://mariantoc.github.io/excursions.html#MillerJB1959</v>
       </c>
     </row>
@@ -50107,7 +50176,7 @@
       <c r="E1373" t="s">
         <v>5033</v>
       </c>
-      <c r="F1373" s="8" t="s">
+      <c r="F1373" t="s">
         <v>5047</v>
       </c>
       <c r="G1373" s="1" t="str">
@@ -50132,7 +50201,7 @@
       <c r="E1374" t="s">
         <v>5036</v>
       </c>
-      <c r="F1374" s="8" t="s">
+      <c r="F1374" t="s">
         <v>5048</v>
       </c>
       <c r="G1374" s="1" t="str">
@@ -50157,7 +50226,7 @@
       <c r="E1375" t="s">
         <v>5016</v>
       </c>
-      <c r="F1375" s="8" t="s">
+      <c r="F1375" t="s">
         <v>5049</v>
       </c>
       <c r="G1375" s="1" t="str">
@@ -50182,7 +50251,7 @@
       <c r="E1376" t="s">
         <v>4738</v>
       </c>
-      <c r="F1376" s="8" t="s">
+      <c r="F1376" t="s">
         <v>5050</v>
       </c>
       <c r="G1376" s="1" t="str">
@@ -50207,7 +50276,7 @@
       <c r="E1377" t="s">
         <v>5040</v>
       </c>
-      <c r="F1377" s="8" t="s">
+      <c r="F1377" t="s">
         <v>5051</v>
       </c>
       <c r="G1377" s="1" t="str">
@@ -50232,7 +50301,7 @@
       <c r="E1378" t="s">
         <v>5043</v>
       </c>
-      <c r="F1378" s="8" t="s">
+      <c r="F1378" t="s">
         <v>5052</v>
       </c>
       <c r="G1378" s="1" t="str">
@@ -50257,7 +50326,7 @@
       <c r="E1379" t="s">
         <v>5046</v>
       </c>
-      <c r="F1379" s="8" t="s">
+      <c r="F1379" t="s">
         <v>5053</v>
       </c>
       <c r="G1379" s="1" t="str">
@@ -50266,38 +50335,172 @@
       </c>
     </row>
     <row r="1380" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1380" s="7" t="s">
-        <v>4315</v>
+      <c r="A1380">
+        <f t="shared" si="43"/>
+        <v>1379</v>
+      </c>
+      <c r="B1380" t="s">
+        <v>5054</v>
+      </c>
+      <c r="C1380" t="s">
+        <v>5055</v>
+      </c>
+      <c r="D1380">
+        <v>2015</v>
+      </c>
+      <c r="E1380" t="s">
+        <v>5056</v>
+      </c>
+      <c r="F1380" s="8" t="s">
+        <v>5070</v>
+      </c>
+      <c r="G1380" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/minerals.html#MorenoACCetal2015</v>
       </c>
     </row>
     <row r="1381" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1381" s="7" t="s">
-        <v>4315</v>
+      <c r="A1381">
+        <f t="shared" si="43"/>
+        <v>1380</v>
+      </c>
+      <c r="B1381" t="s">
+        <v>5057</v>
+      </c>
+      <c r="C1381" t="s">
+        <v>5058</v>
+      </c>
+      <c r="D1381">
+        <v>2026</v>
+      </c>
+      <c r="E1381" t="s">
+        <v>5059</v>
+      </c>
+      <c r="F1381" s="8" t="s">
+        <v>5071</v>
+      </c>
+      <c r="G1381" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/fields.html#PorrasJS2026a</v>
       </c>
     </row>
     <row r="1382" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1382" s="7" t="s">
-        <v>4315</v>
+      <c r="A1382">
+        <f t="shared" si="43"/>
+        <v>1381</v>
+      </c>
+      <c r="B1382" t="s">
+        <v>5060</v>
+      </c>
+      <c r="C1382" t="s">
+        <v>461</v>
+      </c>
+      <c r="D1382">
+        <v>2017</v>
+      </c>
+      <c r="E1382" t="s">
+        <v>5061</v>
+      </c>
+      <c r="F1382" s="8" t="s">
+        <v>5072</v>
+      </c>
+      <c r="G1382" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/biography.html#UrbaniF2017</v>
       </c>
     </row>
     <row r="1383" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1383" s="7" t="s">
-        <v>4315</v>
+      <c r="A1383">
+        <f t="shared" si="43"/>
+        <v>1382</v>
+      </c>
+      <c r="B1383" t="s">
+        <v>5062</v>
+      </c>
+      <c r="C1383" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1383">
+        <v>1998</v>
+      </c>
+      <c r="E1383" t="s">
+        <v>5033</v>
+      </c>
+      <c r="F1383" s="8" t="s">
+        <v>5073</v>
+      </c>
+      <c r="G1383" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#CastroM1998b</v>
       </c>
     </row>
     <row r="1384" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1384" s="7" t="s">
-        <v>4315</v>
+      <c r="A1384">
+        <f t="shared" si="43"/>
+        <v>1383</v>
+      </c>
+      <c r="B1384" t="s">
+        <v>5063</v>
+      </c>
+      <c r="C1384" t="s">
+        <v>5064</v>
+      </c>
+      <c r="D1384">
+        <v>2026</v>
+      </c>
+      <c r="E1384" t="s">
+        <v>5065</v>
+      </c>
+      <c r="F1384" s="8" t="s">
+        <v>5074</v>
+      </c>
+      <c r="G1384" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/minerals.html#MendozaVetal2026</v>
       </c>
     </row>
     <row r="1385" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1385" s="7" t="s">
-        <v>4315</v>
+      <c r="A1385">
+        <f t="shared" si="43"/>
+        <v>1384</v>
+      </c>
+      <c r="B1385" t="s">
+        <v>5066</v>
+      </c>
+      <c r="D1385">
+        <v>1993</v>
+      </c>
+      <c r="E1385" t="s">
+        <v>5067</v>
+      </c>
+      <c r="F1385" s="8" t="s">
+        <v>5075</v>
+      </c>
+      <c r="G1385" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/igneous.html#AgeGranitoides1993</v>
       </c>
     </row>
     <row r="1386" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1386" s="7" t="s">
-        <v>4315</v>
+      <c r="A1386">
+        <f t="shared" si="43"/>
+        <v>1385</v>
+      </c>
+      <c r="B1386" t="s">
+        <v>5068</v>
+      </c>
+      <c r="D1386">
+        <v>2026</v>
+      </c>
+      <c r="E1386" t="s">
+        <v>5069</v>
+      </c>
+      <c r="F1386" s="8" t="s">
+        <v>5076</v>
+      </c>
+      <c r="G1386" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/biography.html#UDO2026</v>
       </c>
     </row>
     <row r="1387" spans="1:7" x14ac:dyDescent="0.3">

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918755D0-25FE-41BC-956B-9ADB073D78EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27C36372-6293-44C9-B0CE-CCE42C2092FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5545" uniqueCount="5077">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5566" uniqueCount="5103">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -15604,6 +15604,84 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/biography.html#UDO2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciencia a golpe de machete. </t>
+  </si>
+  <si>
+    <t>Petroleum, Octubre 6, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La historia de nuestro planeta esta representada por su registro fósil. </t>
+  </si>
+  <si>
+    <t>Charla asignatura Bioestratigrafía, 1997</t>
+  </si>
+  <si>
+    <t>Nueva interpretación paleogeográfica del Eoceno de Barinas.</t>
+  </si>
+  <si>
+    <t>Mounir Mamohoudi; Luisa Figueroa; Clara Guerra; Zorena Monroy</t>
+  </si>
+  <si>
+    <t>República de Venezuela, Ministerio de Energía y Minas, Dirección General Sectorial de Servigeomin, Volumen XVIII, Número 31, Septiembre 1997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taller de núcleos (Core Workshop). Arena “I”, Formación Escandalosa, Formación Gobernador, Formación La Luna, Formación Paují, Formación Misoa, Formación Naricual. </t>
+  </si>
+  <si>
+    <t>Jean Yves Chatellier y Rosa Aquino</t>
+  </si>
+  <si>
+    <t>VIII Congreso Geológico Venezolano. I Congreso Latinoamericano de Sedimentología, Edición Especial de la Sociedad Venezolana de Geólogos, Noviembre 20,1977</t>
+  </si>
+  <si>
+    <t>Alternativa de la minería a cielo abierto en Guasare.</t>
+  </si>
+  <si>
+    <t>Santiago Díaz</t>
+  </si>
+  <si>
+    <t>Memorias I Jornadas Geológicas CarboZulia. Carbones del Zulia C.A., Maracaibo, 1983</t>
+  </si>
+  <si>
+    <t>Excursión Número 4. Sistema Montañoso del Caribe.</t>
+  </si>
+  <si>
+    <t>Luis González Silva. Guías:  Bellizzia, A.; Menéndez, A.; Picard, X; González Silva. L. A.</t>
+  </si>
+  <si>
+    <t>Memoria Segundo Congreso Latinoamericano de Geología, Caracas, Venezuela. 11 al 16 de Noviembre de 1973. Tomo I.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cueva Alfredo Jahn. </t>
+  </si>
+  <si>
+    <t>Roberto E. Contreras y Bertha Contreras Boyer</t>
+  </si>
+  <si>
+    <t>Boletín Informativo de la Sociedad Venezolana de Geólogos, Filial Zulia, Número 8, Maracaibo, Febrero 1988</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#LorenteMA2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#CastroM1997</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#MounirMetal1997</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#ChatellierJYAquinoR1977</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/minerals.html#DiazS1983</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/excursions.html#GonzalezLetal1973</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/speleology.html#ContrerasREContrerasB1988</t>
   </si>
 </sst>
 </file>
@@ -49489,7 +49567,7 @@
     </row>
     <row r="1346" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1346">
-        <f t="shared" ref="A1346:A1386" si="43">A1345+1</f>
+        <f t="shared" ref="A1346:A1393" si="43">A1345+1</f>
         <v>1345</v>
       </c>
       <c r="B1346" t="s">
@@ -49508,7 +49586,7 @@
         <v>4951</v>
       </c>
       <c r="G1346" s="1" t="str">
-        <f t="shared" ref="G1346:G1386" si="44">HYPERLINK(F1346)</f>
+        <f t="shared" ref="G1346:G1393" si="44">HYPERLINK(F1346)</f>
         <v>https://mariantoc.github.io/excursions.html#MillerJB1959</v>
       </c>
     </row>
@@ -50351,7 +50429,7 @@
       <c r="E1380" t="s">
         <v>5056</v>
       </c>
-      <c r="F1380" s="8" t="s">
+      <c r="F1380" t="s">
         <v>5070</v>
       </c>
       <c r="G1380" s="1" t="str">
@@ -50376,7 +50454,7 @@
       <c r="E1381" t="s">
         <v>5059</v>
       </c>
-      <c r="F1381" s="8" t="s">
+      <c r="F1381" t="s">
         <v>5071</v>
       </c>
       <c r="G1381" s="1" t="str">
@@ -50401,7 +50479,7 @@
       <c r="E1382" t="s">
         <v>5061</v>
       </c>
-      <c r="F1382" s="8" t="s">
+      <c r="F1382" t="s">
         <v>5072</v>
       </c>
       <c r="G1382" s="1" t="str">
@@ -50426,7 +50504,7 @@
       <c r="E1383" t="s">
         <v>5033</v>
       </c>
-      <c r="F1383" s="8" t="s">
+      <c r="F1383" t="s">
         <v>5073</v>
       </c>
       <c r="G1383" s="1" t="str">
@@ -50451,7 +50529,7 @@
       <c r="E1384" t="s">
         <v>5065</v>
       </c>
-      <c r="F1384" s="8" t="s">
+      <c r="F1384" t="s">
         <v>5074</v>
       </c>
       <c r="G1384" s="1" t="str">
@@ -50473,7 +50551,7 @@
       <c r="E1385" t="s">
         <v>5067</v>
       </c>
-      <c r="F1385" s="8" t="s">
+      <c r="F1385" t="s">
         <v>5075</v>
       </c>
       <c r="G1385" s="1" t="str">
@@ -50495,7 +50573,7 @@
       <c r="E1386" t="s">
         <v>5069</v>
       </c>
-      <c r="F1386" s="8" t="s">
+      <c r="F1386" t="s">
         <v>5076</v>
       </c>
       <c r="G1386" s="1" t="str">
@@ -50504,111 +50582,251 @@
       </c>
     </row>
     <row r="1387" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1387" s="7" t="s">
-        <v>4315</v>
+      <c r="A1387">
+        <f t="shared" si="43"/>
+        <v>1386</v>
+      </c>
+      <c r="B1387" t="s">
+        <v>5077</v>
+      </c>
+      <c r="C1387" t="s">
+        <v>791</v>
+      </c>
+      <c r="D1387">
+        <v>2026</v>
+      </c>
+      <c r="E1387" t="s">
+        <v>5078</v>
+      </c>
+      <c r="F1387" s="8" t="s">
+        <v>5096</v>
+      </c>
+      <c r="G1387" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/biography.html#LorenteMA2026</v>
       </c>
     </row>
     <row r="1388" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1388" s="7" t="s">
-        <v>4315</v>
+      <c r="A1388">
+        <f t="shared" si="43"/>
+        <v>1387</v>
+      </c>
+      <c r="B1388" t="s">
+        <v>5079</v>
+      </c>
+      <c r="C1388" t="s">
+        <v>2880</v>
+      </c>
+      <c r="D1388">
+        <v>1997</v>
+      </c>
+      <c r="E1388" t="s">
+        <v>5080</v>
+      </c>
+      <c r="F1388" s="8" t="s">
+        <v>5097</v>
+      </c>
+      <c r="G1388" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#CastroM1997</v>
       </c>
     </row>
     <row r="1389" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1389" s="7" t="s">
-        <v>4315</v>
+      <c r="A1389">
+        <f t="shared" si="43"/>
+        <v>1388</v>
+      </c>
+      <c r="B1389" t="s">
+        <v>5081</v>
+      </c>
+      <c r="C1389" t="s">
+        <v>5082</v>
+      </c>
+      <c r="D1389">
+        <v>1997</v>
+      </c>
+      <c r="E1389" t="s">
+        <v>5083</v>
+      </c>
+      <c r="F1389" s="8" t="s">
+        <v>5098</v>
+      </c>
+      <c r="G1389" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#MounirMetal1997</v>
       </c>
     </row>
     <row r="1390" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1390" s="7" t="s">
-        <v>4315</v>
+      <c r="A1390">
+        <f t="shared" si="43"/>
+        <v>1389</v>
+      </c>
+      <c r="B1390" t="s">
+        <v>5084</v>
+      </c>
+      <c r="C1390" t="s">
+        <v>5085</v>
+      </c>
+      <c r="D1390">
+        <v>1977</v>
+      </c>
+      <c r="E1390" t="s">
+        <v>5086</v>
+      </c>
+      <c r="F1390" s="8" t="s">
+        <v>5099</v>
+      </c>
+      <c r="G1390" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#ChatellierJYAquinoR1977</v>
       </c>
     </row>
     <row r="1391" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1391" s="7" t="s">
-        <v>4315</v>
+      <c r="A1391">
+        <f t="shared" si="43"/>
+        <v>1390</v>
+      </c>
+      <c r="B1391" t="s">
+        <v>5087</v>
+      </c>
+      <c r="C1391" t="s">
+        <v>5088</v>
+      </c>
+      <c r="D1391">
+        <v>1983</v>
+      </c>
+      <c r="E1391" t="s">
+        <v>5089</v>
+      </c>
+      <c r="F1391" s="8" t="s">
+        <v>5100</v>
+      </c>
+      <c r="G1391" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/minerals.html#DiazS1983</v>
       </c>
     </row>
     <row r="1392" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1392" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1393" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1393" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1394" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="A1392">
+        <f t="shared" si="43"/>
+        <v>1391</v>
+      </c>
+      <c r="B1392" t="s">
+        <v>5090</v>
+      </c>
+      <c r="C1392" t="s">
+        <v>5091</v>
+      </c>
+      <c r="D1392">
+        <v>1973</v>
+      </c>
+      <c r="E1392" t="s">
+        <v>5092</v>
+      </c>
+      <c r="F1392" s="8" t="s">
+        <v>5101</v>
+      </c>
+      <c r="G1392" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/excursions.html#GonzalezLetal1973</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1393">
+        <f t="shared" si="43"/>
+        <v>1392</v>
+      </c>
+      <c r="B1393" t="s">
+        <v>5093</v>
+      </c>
+      <c r="C1393" t="s">
+        <v>5094</v>
+      </c>
+      <c r="D1393">
+        <v>1988</v>
+      </c>
+      <c r="E1393" t="s">
+        <v>5095</v>
+      </c>
+      <c r="F1393" s="8" t="s">
+        <v>5102</v>
+      </c>
+      <c r="G1393" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/speleology.html#ContrerasREContrerasB1988</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1394" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1395" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1395" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1395" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1396" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1396" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1396" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1397" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1397" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1397" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1398" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1398" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1398" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1399" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1399" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1399" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1400" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1400" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1400" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1401" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1401" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1401" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1402" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1402" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1402" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1403" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1403" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1403" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1404" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1404" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1404" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1405" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1405" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1405" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1406" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1406" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1406" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1407" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1407" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1407" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1408" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1408" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1408" s="7" t="s">
         <v>4315</v>
       </c>

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27C36372-6293-44C9-B0CE-CCE42C2092FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA8A08D5-9DCB-428B-A45E-D66DCFB14D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5566" uniqueCount="5103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5587" uniqueCount="5127">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -15682,6 +15682,78 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/speleology.html#ContrerasREContrerasB1988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes on the shifting course of the ancient Rio Orinoco from Late Cretaceous to Oligocene time. </t>
+  </si>
+  <si>
+    <t>GEOS, Número 81, pp. 30 – 31, 1981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isla de Aves: Equilibrio entre subsidencia, aumento del nivel del mar, acreción y progradación. </t>
+  </si>
+  <si>
+    <t>Boletín de Geología, Volumen XXI, Número 34, Instituto Nacional de Geología y Minería, 2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estratigrafía. </t>
+  </si>
+  <si>
+    <t>Clases de Bioestratigrafía, 1997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisión estratigráfica de la Cuenca de Venezuela oriental. </t>
+  </si>
+  <si>
+    <t>VI Congreso Geológico Venezolano, 29 de Septiembre a 6 de Octubre de 1985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microfacies del Cretácico de Venezuela occidental. </t>
+  </si>
+  <si>
+    <t>A. Ford y J. J. H. C. Houbolt</t>
+  </si>
+  <si>
+    <t>International Sedimentary Petrographical Series. Edited by J. Cuvillier and HME Schűrmann, Volume VI, Leiden, 1963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New oil discoveries in the Ceuta Area, S. E. Lake Maracaibo, Venezuela. </t>
+  </si>
+  <si>
+    <t>From Brooks, J. editor, 1990. Classic Petroleum Provinces, Geological Society, Special Publication, No. 50, pp. 77 – 88</t>
+  </si>
+  <si>
+    <t>M. Roberto; E. Mompart; E. Puche; F. Scherer</t>
+  </si>
+  <si>
+    <t>Energía en el futuro.</t>
+  </si>
+  <si>
+    <t>Gonzalo J. Morales</t>
+  </si>
+  <si>
+    <t>Boletín de la Academia Nacional de la Ingeniería y el Habitat, Nűmero 68, Julio – Septiembre, 2025, pp. 23 – 29, Caracas, Venezuela</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#RodE1981</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#MendezJ2015</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#CastroM1997a</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#ArnsteyRetal1985</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#FordAHouboldtJJHC1963</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/fields.html#RobertoMetal1990</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/ecology.html#MoralesGJ2025</t>
   </si>
 </sst>
 </file>
@@ -49567,7 +49639,7 @@
     </row>
     <row r="1346" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1346">
-        <f t="shared" ref="A1346:A1393" si="43">A1345+1</f>
+        <f t="shared" ref="A1346:A1400" si="43">A1345+1</f>
         <v>1345</v>
       </c>
       <c r="B1346" t="s">
@@ -49586,7 +49658,7 @@
         <v>4951</v>
       </c>
       <c r="G1346" s="1" t="str">
-        <f t="shared" ref="G1346:G1393" si="44">HYPERLINK(F1346)</f>
+        <f t="shared" ref="G1346:G1400" si="44">HYPERLINK(F1346)</f>
         <v>https://mariantoc.github.io/excursions.html#MillerJB1959</v>
       </c>
     </row>
@@ -50598,7 +50670,7 @@
       <c r="E1387" t="s">
         <v>5078</v>
       </c>
-      <c r="F1387" s="8" t="s">
+      <c r="F1387" t="s">
         <v>5096</v>
       </c>
       <c r="G1387" s="1" t="str">
@@ -50623,7 +50695,7 @@
       <c r="E1388" t="s">
         <v>5080</v>
       </c>
-      <c r="F1388" s="8" t="s">
+      <c r="F1388" t="s">
         <v>5097</v>
       </c>
       <c r="G1388" s="1" t="str">
@@ -50648,7 +50720,7 @@
       <c r="E1389" t="s">
         <v>5083</v>
       </c>
-      <c r="F1389" s="8" t="s">
+      <c r="F1389" t="s">
         <v>5098</v>
       </c>
       <c r="G1389" s="1" t="str">
@@ -50673,7 +50745,7 @@
       <c r="E1390" t="s">
         <v>5086</v>
       </c>
-      <c r="F1390" s="8" t="s">
+      <c r="F1390" t="s">
         <v>5099</v>
       </c>
       <c r="G1390" s="1" t="str">
@@ -50698,7 +50770,7 @@
       <c r="E1391" t="s">
         <v>5089</v>
       </c>
-      <c r="F1391" s="8" t="s">
+      <c r="F1391" t="s">
         <v>5100</v>
       </c>
       <c r="G1391" s="1" t="str">
@@ -50723,7 +50795,7 @@
       <c r="E1392" t="s">
         <v>5092</v>
       </c>
-      <c r="F1392" s="8" t="s">
+      <c r="F1392" t="s">
         <v>5101</v>
       </c>
       <c r="G1392" s="1" t="str">
@@ -50748,7 +50820,7 @@
       <c r="E1393" t="s">
         <v>5095</v>
       </c>
-      <c r="F1393" s="8" t="s">
+      <c r="F1393" t="s">
         <v>5102</v>
       </c>
       <c r="G1393" s="1" t="str">
@@ -50757,38 +50829,178 @@
       </c>
     </row>
     <row r="1394" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1394" s="7" t="s">
-        <v>4315</v>
+      <c r="A1394">
+        <f t="shared" si="43"/>
+        <v>1393</v>
+      </c>
+      <c r="B1394" t="s">
+        <v>5103</v>
+      </c>
+      <c r="C1394" t="s">
+        <v>703</v>
+      </c>
+      <c r="D1394">
+        <v>1981</v>
+      </c>
+      <c r="E1394" t="s">
+        <v>5104</v>
+      </c>
+      <c r="F1394" s="8" t="s">
+        <v>5120</v>
+      </c>
+      <c r="G1394" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#RodE1981</v>
       </c>
     </row>
     <row r="1395" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1395" s="7" t="s">
-        <v>4315</v>
+      <c r="A1395">
+        <f t="shared" si="43"/>
+        <v>1394</v>
+      </c>
+      <c r="B1395" t="s">
+        <v>5105</v>
+      </c>
+      <c r="C1395" t="s">
+        <v>1986</v>
+      </c>
+      <c r="D1395">
+        <v>2015</v>
+      </c>
+      <c r="E1395" t="s">
+        <v>5106</v>
+      </c>
+      <c r="F1395" s="8" t="s">
+        <v>5121</v>
+      </c>
+      <c r="G1395" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#MendezJ2015</v>
       </c>
     </row>
     <row r="1396" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1396" s="7" t="s">
-        <v>4315</v>
+      <c r="A1396">
+        <f t="shared" si="43"/>
+        <v>1395</v>
+      </c>
+      <c r="B1396" t="s">
+        <v>5107</v>
+      </c>
+      <c r="C1396" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1396">
+        <v>1997</v>
+      </c>
+      <c r="E1396" t="s">
+        <v>5108</v>
+      </c>
+      <c r="F1396" s="8" t="s">
+        <v>5122</v>
+      </c>
+      <c r="G1396" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#CastroM1997a</v>
       </c>
     </row>
     <row r="1397" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1397" s="7" t="s">
-        <v>4315</v>
+      <c r="A1397">
+        <f t="shared" si="43"/>
+        <v>1396</v>
+      </c>
+      <c r="B1397" t="s">
+        <v>5109</v>
+      </c>
+      <c r="C1397" t="s">
+        <v>242</v>
+      </c>
+      <c r="D1397">
+        <v>1985</v>
+      </c>
+      <c r="E1397" t="s">
+        <v>5110</v>
+      </c>
+      <c r="F1397" s="8" t="s">
+        <v>5123</v>
+      </c>
+      <c r="G1397" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#ArnsteyRetal1985</v>
       </c>
     </row>
     <row r="1398" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1398" s="7" t="s">
-        <v>4315</v>
+      <c r="A1398">
+        <f t="shared" si="43"/>
+        <v>1397</v>
+      </c>
+      <c r="B1398" t="s">
+        <v>5111</v>
+      </c>
+      <c r="C1398" t="s">
+        <v>5112</v>
+      </c>
+      <c r="D1398">
+        <v>1963</v>
+      </c>
+      <c r="E1398" t="s">
+        <v>5113</v>
+      </c>
+      <c r="F1398" s="8" t="s">
+        <v>5124</v>
+      </c>
+      <c r="G1398" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#FordAHouboldtJJHC1963</v>
       </c>
     </row>
     <row r="1399" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1399" s="7" t="s">
-        <v>4315</v>
+      <c r="A1399">
+        <f t="shared" si="43"/>
+        <v>1398</v>
+      </c>
+      <c r="B1399" t="s">
+        <v>5114</v>
+      </c>
+      <c r="C1399" t="s">
+        <v>5116</v>
+      </c>
+      <c r="D1399">
+        <v>1990</v>
+      </c>
+      <c r="E1399" t="s">
+        <v>5115</v>
+      </c>
+      <c r="F1399" s="8" t="s">
+        <v>5125</v>
+      </c>
+      <c r="G1399" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/fields.html#RobertoMetal1990</v>
       </c>
     </row>
     <row r="1400" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1400" s="7" t="s">
-        <v>4315</v>
+      <c r="A1400">
+        <f t="shared" si="43"/>
+        <v>1399</v>
+      </c>
+      <c r="B1400" t="s">
+        <v>5117</v>
+      </c>
+      <c r="C1400" t="s">
+        <v>5118</v>
+      </c>
+      <c r="D1400">
+        <v>2025</v>
+      </c>
+      <c r="E1400" t="s">
+        <v>5119</v>
+      </c>
+      <c r="F1400" s="8" t="s">
+        <v>5126</v>
+      </c>
+      <c r="G1400" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/ecology.html#MoralesGJ2025</v>
       </c>
     </row>
     <row r="1401" spans="1:7" x14ac:dyDescent="0.3">

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA8A08D5-9DCB-428B-A45E-D66DCFB14D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E201CD4-99C4-410A-9C6C-B6620D4F69BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5587" uniqueCount="5127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5607" uniqueCount="5151">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -15754,6 +15754,78 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/ecology.html#MoralesGJ2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evolución sedimentológica del abanico aluvial de Caraballeda, estado Vargas, Venezuela. </t>
+  </si>
+  <si>
+    <t>Edgar Chacín Benedetto y Amarilis Esteves Albarrán</t>
+  </si>
+  <si>
+    <t>PetroRenova (Indexed). Revista Científica de la Energía, Volumen 2, Número 4, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reconstrucción del sector hidrocarburos en Venezuela. Viabilidad, Inversión y Confiabilidad. </t>
+  </si>
+  <si>
+    <t>Jorge García</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unidades Litoestratigráficas. </t>
+  </si>
+  <si>
+    <t>Charla en las clases de Bioestratigrafía, 1997</t>
+  </si>
+  <si>
+    <t>Excursión Geológica No. 3. Sierra de Perijá.</t>
+  </si>
+  <si>
+    <t>Alejandrino Nogueira</t>
+  </si>
+  <si>
+    <t>Memoria Segundo Congreso Latinoamericano de Geología, Tomo 1. 11 al 16 de Noviembre de 1973, Caracas, Venezuela</t>
+  </si>
+  <si>
+    <t>Revista GEOS, Número 1, Caracas, Venezuela, Enero 1959</t>
+  </si>
+  <si>
+    <t>Parques Nacionales y Monumentos Naturales de Venezuela.</t>
+  </si>
+  <si>
+    <t>Instituto Nacional de Parques. Editado por el Ministerio del Ambiente y de los Recursos Naturales Renovables, Diciembre 1978, Caracas, Venezuela</t>
+  </si>
+  <si>
+    <t>Introducción al estudio de los macroforaminíferos de la familia Orbitolinidae.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Great Geologists. </t>
+  </si>
+  <si>
+    <t>Mike Simmons</t>
+  </si>
+  <si>
+    <t>Halliburton, United Kingdom, 2018</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#ChacinEEstevesA2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/fields.html#GarciaJ2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#CastroM1997b</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/excursions.html#NogueiraA1973</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#CharltonF1959</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/ecology.html#Inparques1978</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#SimmonsM2018</t>
   </si>
 </sst>
 </file>
@@ -49639,7 +49711,7 @@
     </row>
     <row r="1346" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1346">
-        <f t="shared" ref="A1346:A1400" si="43">A1345+1</f>
+        <f t="shared" ref="A1346:A1407" si="43">A1345+1</f>
         <v>1345</v>
       </c>
       <c r="B1346" t="s">
@@ -49658,7 +49730,7 @@
         <v>4951</v>
       </c>
       <c r="G1346" s="1" t="str">
-        <f t="shared" ref="G1346:G1400" si="44">HYPERLINK(F1346)</f>
+        <f t="shared" ref="G1346:G1407" si="44">HYPERLINK(F1346)</f>
         <v>https://mariantoc.github.io/excursions.html#MillerJB1959</v>
       </c>
     </row>
@@ -50845,7 +50917,7 @@
       <c r="E1394" t="s">
         <v>5104</v>
       </c>
-      <c r="F1394" s="8" t="s">
+      <c r="F1394" t="s">
         <v>5120</v>
       </c>
       <c r="G1394" s="1" t="str">
@@ -50870,7 +50942,7 @@
       <c r="E1395" t="s">
         <v>5106</v>
       </c>
-      <c r="F1395" s="8" t="s">
+      <c r="F1395" t="s">
         <v>5121</v>
       </c>
       <c r="G1395" s="1" t="str">
@@ -50895,7 +50967,7 @@
       <c r="E1396" t="s">
         <v>5108</v>
       </c>
-      <c r="F1396" s="8" t="s">
+      <c r="F1396" t="s">
         <v>5122</v>
       </c>
       <c r="G1396" s="1" t="str">
@@ -50920,7 +50992,7 @@
       <c r="E1397" t="s">
         <v>5110</v>
       </c>
-      <c r="F1397" s="8" t="s">
+      <c r="F1397" t="s">
         <v>5123</v>
       </c>
       <c r="G1397" s="1" t="str">
@@ -50945,7 +51017,7 @@
       <c r="E1398" t="s">
         <v>5113</v>
       </c>
-      <c r="F1398" s="8" t="s">
+      <c r="F1398" t="s">
         <v>5124</v>
       </c>
       <c r="G1398" s="1" t="str">
@@ -50970,7 +51042,7 @@
       <c r="E1399" t="s">
         <v>5115</v>
       </c>
-      <c r="F1399" s="8" t="s">
+      <c r="F1399" t="s">
         <v>5125</v>
       </c>
       <c r="G1399" s="1" t="str">
@@ -50995,7 +51067,7 @@
       <c r="E1400" t="s">
         <v>5119</v>
       </c>
-      <c r="F1400" s="8" t="s">
+      <c r="F1400" t="s">
         <v>5126</v>
       </c>
       <c r="G1400" s="1" t="str">
@@ -51004,38 +51076,175 @@
       </c>
     </row>
     <row r="1401" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1401" s="7" t="s">
-        <v>4315</v>
+      <c r="A1401">
+        <f t="shared" si="43"/>
+        <v>1400</v>
+      </c>
+      <c r="B1401" t="s">
+        <v>5127</v>
+      </c>
+      <c r="C1401" t="s">
+        <v>5128</v>
+      </c>
+      <c r="D1401">
+        <v>2026</v>
+      </c>
+      <c r="E1401" t="s">
+        <v>5129</v>
+      </c>
+      <c r="F1401" s="8" t="s">
+        <v>5144</v>
+      </c>
+      <c r="G1401" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#ChacinEEstevesA2026</v>
       </c>
     </row>
     <row r="1402" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1402" s="7" t="s">
-        <v>4315</v>
+      <c r="A1402">
+        <f t="shared" si="43"/>
+        <v>1401</v>
+      </c>
+      <c r="B1402" t="s">
+        <v>5130</v>
+      </c>
+      <c r="C1402" t="s">
+        <v>5131</v>
+      </c>
+      <c r="D1402">
+        <v>2026</v>
+      </c>
+      <c r="E1402" t="s">
+        <v>5129</v>
+      </c>
+      <c r="F1402" s="8" t="s">
+        <v>5145</v>
+      </c>
+      <c r="G1402" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/fields.html#GarciaJ2026</v>
       </c>
     </row>
     <row r="1403" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1403" s="7" t="s">
-        <v>4315</v>
+      <c r="A1403">
+        <f t="shared" si="43"/>
+        <v>1402</v>
+      </c>
+      <c r="B1403" t="s">
+        <v>5132</v>
+      </c>
+      <c r="C1403" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1403">
+        <v>1997</v>
+      </c>
+      <c r="E1403" t="s">
+        <v>5133</v>
+      </c>
+      <c r="F1403" s="8" t="s">
+        <v>5146</v>
+      </c>
+      <c r="G1403" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#CastroM1997b</v>
       </c>
     </row>
     <row r="1404" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1404" s="7" t="s">
-        <v>4315</v>
+      <c r="A1404">
+        <f t="shared" si="43"/>
+        <v>1403</v>
+      </c>
+      <c r="B1404" t="s">
+        <v>5134</v>
+      </c>
+      <c r="C1404" t="s">
+        <v>5135</v>
+      </c>
+      <c r="D1404">
+        <v>1973</v>
+      </c>
+      <c r="E1404" t="s">
+        <v>5136</v>
+      </c>
+      <c r="F1404" s="8" t="s">
+        <v>5147</v>
+      </c>
+      <c r="G1404" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/excursions.html#NogueiraA1973</v>
       </c>
     </row>
     <row r="1405" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1405" s="7" t="s">
-        <v>4315</v>
+      <c r="A1405">
+        <f t="shared" si="43"/>
+        <v>1404</v>
+      </c>
+      <c r="B1405" t="s">
+        <v>5140</v>
+      </c>
+      <c r="C1405" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D1405">
+        <v>1959</v>
+      </c>
+      <c r="E1405" t="s">
+        <v>5137</v>
+      </c>
+      <c r="F1405" s="8" t="s">
+        <v>5148</v>
+      </c>
+      <c r="G1405" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#CharltonF1959</v>
       </c>
     </row>
     <row r="1406" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1406" s="7" t="s">
-        <v>4315</v>
+      <c r="A1406">
+        <f t="shared" si="43"/>
+        <v>1405</v>
+      </c>
+      <c r="B1406" t="s">
+        <v>5138</v>
+      </c>
+      <c r="D1406">
+        <v>1978</v>
+      </c>
+      <c r="E1406" t="s">
+        <v>5139</v>
+      </c>
+      <c r="F1406" s="8" t="s">
+        <v>5149</v>
+      </c>
+      <c r="G1406" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/ecology.html#Inparques1978</v>
       </c>
     </row>
     <row r="1407" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1407" s="7" t="s">
-        <v>4315</v>
+      <c r="A1407">
+        <f t="shared" si="43"/>
+        <v>1406</v>
+      </c>
+      <c r="B1407" t="s">
+        <v>5141</v>
+      </c>
+      <c r="C1407" t="s">
+        <v>5142</v>
+      </c>
+      <c r="D1407">
+        <v>2018</v>
+      </c>
+      <c r="E1407" t="s">
+        <v>5143</v>
+      </c>
+      <c r="F1407" s="8" t="s">
+        <v>5150</v>
+      </c>
+      <c r="G1407" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>https://mariantoc.github.io/biography.html#SimmonsM2018</v>
       </c>
     </row>
     <row r="1408" spans="1:7" x14ac:dyDescent="0.3">
